--- a/KandRStyle/research/risk_air_gap/ComputerCrime_CALIFORNIA_JUL2026.xlsx
+++ b/KandRStyle/research/risk_air_gap/ComputerCrime_CALIFORNIA_JUL2026.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladi\source\repos\bookWork2\KandRStyle\research\risk_air_gap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3456C58-F0AB-4BC5-BEAB-663F9A8D7CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF86946A-BB6A-47BE-A9EB-88B7FD10DE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{A6B90A6B-86D8-4A34-B9C9-776670F3C0EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="8" xr2:uid="{A6B90A6B-86D8-4A34-B9C9-776670F3C0EC}"/>
   </bookViews>
   <sheets>
-    <sheet name="State Summary Graphs" sheetId="13" r:id="rId1"/>
-    <sheet name="2016_IC3 State to City" sheetId="11" r:id="rId2"/>
-    <sheet name="2017_IC3 State to City" sheetId="10" r:id="rId3"/>
-    <sheet name="2018_IC3 State to City" sheetId="9" r:id="rId4"/>
-    <sheet name="2019_IC3 State to City" sheetId="8" r:id="rId5"/>
-    <sheet name="2020_IC3 State to City" sheetId="7" r:id="rId6"/>
-    <sheet name="2021_IC3 State to City" sheetId="6" r:id="rId7"/>
-    <sheet name="City Summary" sheetId="12" r:id="rId8"/>
-    <sheet name="2022_IC3 State to City" sheetId="3" r:id="rId9"/>
-    <sheet name="BLANK_IC3 State to City" sheetId="4" r:id="rId10"/>
-    <sheet name="BLANK_IC3 State to City (2)" sheetId="5" r:id="rId11"/>
+    <sheet name="State Summary Graphs CALIFORNIA" sheetId="13" r:id="rId1"/>
+    <sheet name="2016_IC3 State to City CALIFORN" sheetId="11" r:id="rId2"/>
+    <sheet name="2017_IC3 State to City CALIFORN" sheetId="10" r:id="rId3"/>
+    <sheet name="2018_IC3 State to City CALIFORN" sheetId="9" r:id="rId4"/>
+    <sheet name="2019_IC3 State to City CALIFORN" sheetId="8" r:id="rId5"/>
+    <sheet name="2020_IC3 State to City CALIFORN" sheetId="7" r:id="rId6"/>
+    <sheet name="2021_IC3 State to City CALIFORN" sheetId="6" r:id="rId7"/>
+    <sheet name="City Summary CALIFORNIA" sheetId="12" r:id="rId8"/>
+    <sheet name="2022_IC3 State to City CALIFORN" sheetId="3" r:id="rId9"/>
+    <sheet name="BLANK_IC3 State to City CALIFOR" sheetId="4" r:id="rId10"/>
+    <sheet name="BLANK_IC3 State to City (2) CAL" sheetId="5" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -415,7 +415,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000000000000000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -509,15 +509,15 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -625,7 +625,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$I$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$I$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -708,7 +708,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -738,7 +738,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$I$5:$I$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$I$5:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -967,7 +967,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$J$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$J$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1050,7 +1050,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1080,7 +1080,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$J$5:$J$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$J$5:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1309,7 +1309,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$K$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$K$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1392,7 +1392,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1422,7 +1422,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$K$5:$K$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$K$5:$K$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1651,7 +1651,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$L$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$L$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1734,7 +1734,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1764,7 +1764,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$L$5:$L$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$L$5:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2026,7 +2026,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$H$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$H$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2113,7 +2113,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2143,7 +2143,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$H$5:$H$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$H$5:$H$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2183,7 +2183,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$I$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$I$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2270,7 +2270,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$B$5:$B$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2300,7 +2300,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$I$5:$I$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$I$5:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2340,7 +2340,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$J$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$J$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2427,7 +2427,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$J$5:$J$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$J$5:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2467,7 +2467,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$K$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$K$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2554,7 +2554,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$K$5:$K$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$K$5:$K$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2594,7 +2594,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'State Summary Graphs'!$L$4</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$L$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2681,7 +2681,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'State Summary Graphs'!$L$5:$L$11</c:f>
+              <c:f>'State Summary Graphs CALIFORNIA'!$L$5:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -6286,23 +6286,23 @@
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17" t="s">
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17" t="s">
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
@@ -6362,7 +6362,7 @@
         <v>2016</v>
       </c>
       <c r="C5" s="1">
-        <f>'2016_IC3 State to City'!$E$6</f>
+        <f>'2016_IC3 State to City CALIFORN'!$E$6</f>
         <v>177746</v>
       </c>
       <c r="H5" s="1">
@@ -6404,7 +6404,7 @@
         <v>2017</v>
       </c>
       <c r="C6" s="1">
-        <f>'2017_IC3 State to City'!$E$6</f>
+        <f>'2017_IC3 State to City CALIFORN'!$E$6</f>
         <v>179530</v>
       </c>
       <c r="H6" s="1">
@@ -6446,7 +6446,7 @@
         <v>2018</v>
       </c>
       <c r="C7" s="1">
-        <f>'2018_IC3 State to City'!$E$6</f>
+        <f>'2018_IC3 State to City CALIFORN'!$E$6</f>
         <v>181918</v>
       </c>
       <c r="H7" s="1">
@@ -6488,7 +6488,7 @@
         <v>2019</v>
       </c>
       <c r="C8" s="1">
-        <f>'2019_IC3 State to City'!$E$6</f>
+        <f>'2019_IC3 State to City CALIFORN'!$E$6</f>
         <v>182799</v>
       </c>
       <c r="H8" s="1">
@@ -6530,7 +6530,7 @@
         <v>2020</v>
       </c>
       <c r="C9" s="1">
-        <f>'2020_IC3 State to City'!$E$6</f>
+        <f>'2020_IC3 State to City CALIFORN'!$E$6</f>
         <v>181560</v>
       </c>
       <c r="H9" s="1">
@@ -6572,7 +6572,7 @@
         <v>2021</v>
       </c>
       <c r="C10" s="1">
-        <f>'2021_IC3 State to City'!$E$6</f>
+        <f>'2021_IC3 State to City CALIFORN'!$E$6</f>
         <v>181163</v>
       </c>
       <c r="H10" s="1">
@@ -6614,7 +6614,7 @@
         <v>2022</v>
       </c>
       <c r="C11" s="1">
-        <f>'2022_IC3 State to City'!$E$6</f>
+        <f>'2022_IC3 State to City CALIFORN'!$E$6</f>
         <v>184086</v>
       </c>
       <c r="H11" s="1">
@@ -6648,7 +6648,7 @@
         <v>539</v>
       </c>
       <c r="R11" s="1">
-        <f>'2022_IC3 State to City'!$E$8</f>
+        <f>'2022_IC3 State to City CALIFORN'!$E$8</f>
         <v>3269</v>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="H37" s="18"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="7" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -11512,7 +11512,7 @@
         <f>SUM(G8:G36)</f>
         <v>#REF!</v>
       </c>
-      <c r="H38" s="18"/>
+      <c r="H38" s="17"/>
       <c r="I38" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -11530,13 +11530,13 @@
       <c r="C39" t="s">
         <v>79</v>
       </c>
-      <c r="H39" s="18"/>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>76</v>
       </c>
-      <c r="H40" s="18"/>
+      <c r="H40" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11951,7 +11951,7 @@
         <f>ROUNDDOWN(F12*E6,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="19">
         <v>1050</v>
       </c>
       <c r="I12" s="7">
@@ -13473,11 +13473,11 @@
         <v>1134</v>
       </c>
       <c r="L7" s="3">
-        <f>K7/$E$5</f>
+        <f t="shared" ref="L7:L36" si="0">K7/$E$5</f>
         <v>2.8754385138820924E-5</v>
       </c>
       <c r="M7" s="1">
-        <f>ROUNDDOWN(L7*$E$6,0)</f>
+        <f t="shared" ref="M7:M36" si="1">ROUNDDOWN(L7*$E$6,0)</f>
         <v>5</v>
       </c>
       <c r="N7" s="10">
@@ -13519,29 +13519,29 @@
         <v>62675.859168865434</v>
       </c>
       <c r="J8" s="7">
-        <f t="shared" ref="J8:J18" si="0">I8*G8</f>
+        <f t="shared" ref="J8:J18" si="2">I8*G8</f>
         <v>814786.16919525061</v>
       </c>
       <c r="K8" s="1">
         <v>464</v>
       </c>
       <c r="L8" s="3">
-        <f>K8/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.1765462702304152E-5</v>
       </c>
       <c r="M8" s="1">
-        <f>ROUNDDOWN(L8*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N8" s="10">
         <v>32314208</v>
       </c>
       <c r="O8" s="10">
-        <f t="shared" ref="O8:O36" si="1">N8/K8</f>
+        <f t="shared" ref="O8:O36" si="3">N8/K8</f>
         <v>69642.68965517242</v>
       </c>
       <c r="P8" s="7">
-        <f t="shared" ref="P8:P36" si="2">M8*O8</f>
+        <f t="shared" ref="P8:P36" si="4">M8*O8</f>
         <v>139285.37931034484</v>
       </c>
     </row>
@@ -13564,29 +13564,29 @@
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="7" t="e">
-        <f t="shared" ref="I9:I38" si="3">H9/E9</f>
+        <f t="shared" ref="I9:I38" si="5">H9/E9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="3">
-        <f>K9/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f>ROUNDDOWN(L9*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -13613,33 +13613,33 @@
         <v>72355475</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>34373.147268408553</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>309358.32541567698</v>
       </c>
       <c r="K10" s="1">
         <v>1045</v>
       </c>
       <c r="L10" s="3">
-        <f>K10/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.6497647680835858E-5</v>
       </c>
       <c r="M10" s="1">
-        <f>ROUNDDOWN(L10*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N10" s="10">
         <v>44632796</v>
       </c>
       <c r="O10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42710.809569377991</v>
       </c>
       <c r="P10" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170843.23827751196</v>
       </c>
     </row>
@@ -13664,33 +13664,33 @@
         <v>16616018</v>
       </c>
       <c r="I11" s="7" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J11" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K11" s="1">
         <v>861</v>
       </c>
       <c r="L11" s="3">
-        <f>K11/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.1832033160956627E-5</v>
       </c>
       <c r="M11" s="1">
-        <f>ROUNDDOWN(L11*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N11" s="10">
         <v>9737494</v>
       </c>
       <c r="O11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11309.516840882694</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>33928.550522648082</v>
       </c>
     </row>
@@ -13721,29 +13721,29 @@
         <v>86.119402985074629</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12" s="1">
         <v>46</v>
       </c>
       <c r="L12" s="3">
-        <f>K12/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.1664036299698081E-6</v>
       </c>
       <c r="M12" s="1">
-        <f>ROUNDDOWN(L12*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N12" s="10">
         <v>247032</v>
       </c>
       <c r="O12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5370.260869565217</v>
       </c>
       <c r="P12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -13774,27 +13774,27 @@
         <v>33527.267532467529</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>33527.267532467529</v>
       </c>
       <c r="K13" s="1">
         <v>98</v>
       </c>
       <c r="L13" s="3">
-        <f>K13/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.4849468638487219E-6</v>
       </c>
       <c r="M13" s="1">
-        <f>ROUNDDOWN(L13*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N13" s="10"/>
       <c r="O13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P13" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -13821,22 +13821,22 @@
         <v>8608720</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3998.4765443567117</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>35986.288899210405</v>
       </c>
       <c r="K14" s="1">
         <v>1017</v>
       </c>
       <c r="L14" s="3">
-        <f>K14/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.5787662862593366E-5</v>
       </c>
       <c r="M14" s="1">
-        <f>ROUNDDOWN(L14*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N14" s="11">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -13871,22 +13871,22 @@
         <v>24641667</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3007.6488465763455</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>111283.00732332478</v>
       </c>
       <c r="K15" s="1">
         <v>875</v>
       </c>
       <c r="L15" s="3">
-        <f>K15/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.2187025570077871E-5</v>
       </c>
       <c r="M15" s="1">
-        <f>ROUNDDOWN(L15*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N15" s="11">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -13921,33 +13921,33 @@
         <v>19356458</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13935.534917206624</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>83613.209503239748</v>
       </c>
       <c r="K16" s="1">
         <v>252</v>
       </c>
       <c r="L16" s="3">
-        <f>K16/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.3898633641824273E-6</v>
       </c>
       <c r="M16" s="1">
-        <f>ROUNDDOWN(L16*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N16" s="10">
         <v>3276305</v>
       </c>
       <c r="O16" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13001.210317460318</v>
       </c>
       <c r="P16" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13001.210317460318</v>
       </c>
     </row>
@@ -13970,29 +13970,29 @@
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="7" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="3">
-        <f>K17/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f>ROUNDDOWN(L17*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14019,22 +14019,22 @@
         <v>1644275</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4879.1543026706231</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4879.1543026706231</v>
       </c>
       <c r="K18" s="1">
         <v>167</v>
       </c>
       <c r="L18" s="3">
-        <f>K18/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.2345523088034339E-6</v>
       </c>
       <c r="M18" s="1">
-        <f>ROUNDDOWN(L18*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N18" s="11">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -14069,33 +14069,33 @@
         <v>25815846</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12281.563273073263</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" ref="J8:J38" si="4">I19*G19</f>
+        <f t="shared" ref="J19:J38" si="6">I19*G19</f>
         <v>110534.06945765937</v>
       </c>
       <c r="K19" s="1">
         <v>731</v>
       </c>
       <c r="L19" s="3">
-        <f>K19/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.8535675076259343E-5</v>
       </c>
       <c r="M19" s="1">
-        <f>ROUNDDOWN(L19*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N19" s="10">
         <v>9105375</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12456.053351573188</v>
       </c>
       <c r="P19" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>37368.160054719563</v>
       </c>
     </row>
@@ -14122,33 +14122,33 @@
         <v>33707734</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>88938.612137203163</v>
       </c>
       <c r="J20" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>88938.612137203163</v>
       </c>
       <c r="K20" s="1">
         <v>246</v>
       </c>
       <c r="L20" s="3">
-        <f>K20/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.2377237602733217E-6</v>
       </c>
       <c r="M20" s="1">
-        <f>ROUNDDOWN(L20*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N20" s="10">
         <v>38192346</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>155253.43902439025</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>155253.43902439025</v>
       </c>
     </row>
@@ -14173,33 +14173,33 @@
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J21" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K21" s="1">
         <v>256</v>
       </c>
       <c r="L21" s="3">
-        <f>K21/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.4912897667884974E-6</v>
       </c>
       <c r="M21" s="1">
-        <f>ROUNDDOWN(L21*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N21" s="10">
         <v>3818887</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14917.52734375</v>
       </c>
       <c r="P21" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14917.52734375</v>
       </c>
     </row>
@@ -14226,31 +14226,31 @@
         <v>269097</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>649.99275362318838</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>649.99275362318838</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="3">
-        <f>K22/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <f>ROUNDDOWN(L22*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N22" s="10">
         <v>35732</v>
       </c>
       <c r="O22" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P22" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14273,29 +14273,29 @@
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="7" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="3">
-        <f>K23/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f>ROUNDDOWN(L23*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14318,29 +14318,29 @@
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="7" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="3">
-        <f>K24/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>ROUNDDOWN(L24*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14367,31 +14367,31 @@
         <v>70150</v>
       </c>
       <c r="I25" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>11.954669393319699</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>322.77607361963186</v>
       </c>
       <c r="K25" s="1">
         <v>820</v>
       </c>
       <c r="L25" s="3">
-        <f>K25/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.0792412534244406E-5</v>
       </c>
       <c r="M25" s="1">
-        <f>ROUNDDOWN(L25*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N25" s="10"/>
       <c r="O25" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P25" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -14418,33 +14418,33 @@
         <v>26046807</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3002.1677040110649</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>120086.70816044259</v>
       </c>
       <c r="K26" s="1">
         <v>3924</v>
       </c>
       <c r="L26" s="3">
-        <f>K26/$E$5</f>
+        <f t="shared" si="0"/>
         <v>9.9499300956554942E-5</v>
       </c>
       <c r="M26" s="1">
-        <f>ROUNDDOWN(L26*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="N26" s="10">
         <v>18266248</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4655.0071355759428</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>83790.128440366971</v>
       </c>
     </row>
@@ -14471,22 +14471,22 @@
         <v>4841038</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3732.4888203546648</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18662.444101773322</v>
       </c>
       <c r="K27" s="1">
         <v>826</v>
       </c>
       <c r="L27" s="3">
-        <f>K27/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.0944552138153511E-5</v>
       </c>
       <c r="M27" s="1">
-        <f>ROUNDDOWN(L27*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N27" s="10">
@@ -14497,7 +14497,7 @@
         <v>2784.8910411622278</v>
       </c>
       <c r="P27" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8354.6731234866838</v>
       </c>
     </row>
@@ -14524,29 +14524,29 @@
         <v>9649604</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4150.3673118279567</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>41503.673118279563</v>
       </c>
       <c r="K28" s="1">
         <v>1028</v>
       </c>
       <c r="L28" s="3">
-        <f>K28/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.6066585469760059E-5</v>
       </c>
       <c r="M28" s="1">
-        <f>ROUNDDOWN(L28*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N28" s="10">
         <v>4946650</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4811.9163424124517</v>
       </c>
       <c r="P28" s="7">
@@ -14577,33 +14577,33 @@
         <v>26974510</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3378.1477770820288</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>121613.31997495303</v>
       </c>
       <c r="K29" s="1">
         <v>2068</v>
       </c>
       <c r="L29" s="3">
-        <f>K29/$E$5</f>
+        <f t="shared" si="0"/>
         <v>5.2437450147338329E-5</v>
       </c>
       <c r="M29" s="1">
-        <f>ROUNDDOWN(L29*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N29" s="10">
         <v>12780450</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6180.101547388781</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>55620.91392649903</v>
       </c>
     </row>
@@ -14630,33 +14630,33 @@
         <v>7177488</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2603.3688792165399</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31240.42655059848</v>
       </c>
       <c r="K30" s="1">
         <v>800</v>
       </c>
       <c r="L30" s="3">
-        <f>K30/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.0285280521214056E-5</v>
       </c>
       <c r="M30" s="1">
-        <f>ROUNDDOWN(L30*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N30" s="10">
         <v>1064673</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1330.8412499999999</v>
       </c>
       <c r="P30" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3992.5237499999998</v>
       </c>
     </row>
@@ -14687,29 +14687,29 @@
         <v>605.98104265402844</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>19</v>
       </c>
       <c r="L31" s="3">
-        <f>K31/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.8177541237883384E-7</v>
       </c>
       <c r="M31" s="1">
-        <f>ROUNDDOWN(L31*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N31" s="10">
         <v>146</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.6842105263157894</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -14736,33 +14736,33 @@
         <v>24961906</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>11173.637421665175</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>111736.37421665175</v>
       </c>
       <c r="K32" s="1">
         <v>894</v>
       </c>
       <c r="L32" s="3">
-        <f>K32/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.2668800982456706E-5</v>
       </c>
       <c r="M32" s="1">
-        <f>ROUNDDOWN(L32*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N32" s="10">
         <v>10620224</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11879.445190156599</v>
       </c>
       <c r="P32" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>47517.780760626396</v>
       </c>
     </row>
@@ -14785,29 +14785,29 @@
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="7" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="3">
-        <f>K33/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f>ROUNDDOWN(L33*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14834,33 +14834,33 @@
         <v>14684620</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9098.2775712515486</v>
       </c>
       <c r="J34" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>63687.942998760838</v>
       </c>
       <c r="K34" s="1">
         <v>497</v>
       </c>
       <c r="L34" s="3">
-        <f>K34/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.2602230523804231E-5</v>
       </c>
       <c r="M34" s="1">
-        <f>ROUNDDOWN(L34*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N34" s="10">
         <v>3938008</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7923.5573440643866</v>
       </c>
       <c r="P34" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15847.114688128773</v>
       </c>
     </row>
@@ -14887,33 +14887,33 @@
         <v>6815758</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3452.7649442755824</v>
       </c>
       <c r="J35" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31074.884498480242</v>
       </c>
       <c r="K35" s="1">
         <v>752</v>
       </c>
       <c r="L35" s="3">
-        <f>K35/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.9068163689941211E-5</v>
       </c>
       <c r="M35" s="1">
-        <f>ROUNDDOWN(L35*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N35" s="10">
         <v>3258451</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4333.0465425531911</v>
       </c>
       <c r="P35" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12999.139627659573</v>
       </c>
     </row>
@@ -14940,39 +14940,39 @@
         <v>3946923</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1459.6608727810651</v>
       </c>
       <c r="J36" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>17515.93047337278</v>
       </c>
       <c r="K36" s="1">
         <v>1189</v>
       </c>
       <c r="L36" s="3">
-        <f>K36/$E$5</f>
+        <f t="shared" si="0"/>
         <v>3.0148998174654389E-5</v>
       </c>
       <c r="M36" s="1">
-        <f>ROUNDDOWN(L36*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="N36" s="10">
         <v>637271</v>
       </c>
       <c r="O36" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>535.97224558452479</v>
       </c>
       <c r="P36" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2679.861227922624</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="J37" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L37" s="3"/>
@@ -14986,11 +14986,11 @@
         <v>60757</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L38" s="3"/>
@@ -15145,40 +15145,40 @@
         <v>3.9581506080109798E-5</v>
       </c>
       <c r="G7" s="1">
-        <f>ROUNDDOWN(F7*$E$6,0)</f>
+        <f t="shared" ref="G7:G36" si="0">ROUNDDOWN(F7*$E$6,0)</f>
         <v>7</v>
       </c>
       <c r="H7" s="10">
         <v>13542429</v>
       </c>
       <c r="I7" s="7">
-        <f>H7/E7</f>
+        <f t="shared" ref="I7:I36" si="1">H7/E7</f>
         <v>8675.4830237027545</v>
       </c>
       <c r="J7" s="7">
-        <f>I7*G7</f>
+        <f t="shared" ref="J7:J36" si="2">I7*G7</f>
         <v>60728.38116591928</v>
       </c>
       <c r="K7" s="1">
         <v>896</v>
       </c>
       <c r="L7" s="3">
-        <f>K7/$E$5</f>
+        <f t="shared" ref="L7:L36" si="3">K7/$E$5</f>
         <v>2.2719429498897118E-5</v>
       </c>
       <c r="M7" s="1">
-        <f>ROUNDDOWN(L7*$E$6,0)</f>
+        <f t="shared" ref="M7:M36" si="4">ROUNDDOWN(L7*$E$6,0)</f>
         <v>4</v>
       </c>
       <c r="N7" s="10">
         <v>7547188</v>
       </c>
       <c r="O7" s="7">
-        <f>N7/K7</f>
+        <f t="shared" ref="O7:O36" si="5">N7/K7</f>
         <v>8423.2008928571431</v>
       </c>
       <c r="P7" s="7">
-        <f>M7*O7</f>
+        <f t="shared" ref="P7:P36" si="6">M7*O7</f>
         <v>33692.803571428572</v>
       </c>
     </row>
@@ -15199,38 +15199,38 @@
         <v>8.9330971121221605E-5</v>
       </c>
       <c r="G8" s="1">
-        <f>ROUNDDOWN(F8*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="7">
-        <f>H8/E8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="7">
-        <f>I8*G8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>562</v>
       </c>
       <c r="L8" s="3">
-        <f>K8/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.4250356449085023E-5</v>
       </c>
       <c r="M8" s="1">
-        <f>ROUNDDOWN(L8*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="N8" s="10">
         <v>31095390</v>
       </c>
       <c r="O8" s="7">
-        <f>N8/K8</f>
+        <f t="shared" si="5"/>
         <v>55329.875444839854</v>
       </c>
       <c r="P8" s="7">
-        <f>M8*O8</f>
+        <f t="shared" si="6"/>
         <v>110659.75088967971</v>
       </c>
     </row>
@@ -15249,34 +15249,34 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <f>ROUNDDOWN(F9*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="7" t="e">
-        <f>H9/E9</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="7" t="e">
-        <f>I9*G9</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="3">
-        <f>K9/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f>ROUNDDOWN(L9*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="7" t="e">
-        <f>N9/K9</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="7" t="e">
-        <f>M9*O9</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15297,40 +15297,40 @@
         <v>5.5936452538579297E-5</v>
       </c>
       <c r="G10" s="1">
-        <f>ROUNDDOWN(F10*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H10" s="10">
         <v>107853977</v>
       </c>
       <c r="I10" s="7">
-        <f>H10/E10</f>
+        <f t="shared" si="1"/>
         <v>48891.1953762466</v>
       </c>
       <c r="J10" s="7">
-        <f>I10*G10</f>
+        <f t="shared" si="2"/>
         <v>488911.95376246597</v>
       </c>
       <c r="K10" s="1">
         <v>1110</v>
       </c>
       <c r="L10" s="3">
-        <f>K10/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.8145721812249778E-5</v>
       </c>
       <c r="M10" s="1">
-        <f>ROUNDDOWN(L10*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="N10" s="10">
         <v>46198807</v>
       </c>
       <c r="O10" s="7">
-        <f>N10/K10</f>
+        <f t="shared" si="5"/>
         <v>41620.546846846846</v>
       </c>
       <c r="P10" s="7">
-        <f>M10*O10</f>
+        <f t="shared" si="6"/>
         <v>208102.73423423423</v>
       </c>
     </row>
@@ -15351,40 +15351,40 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <f>ROUNDDOWN(F11*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H11" s="11">
         <v>17519988</v>
       </c>
       <c r="I11" s="7">
-        <f>H11/E11</f>
+        <f t="shared" si="1"/>
         <v>8911.4893184130215</v>
       </c>
       <c r="J11" s="7">
-        <f>I11*G11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="1">
         <v>906</v>
       </c>
       <c r="L11" s="3">
-        <f>K11/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.2972994560268739E-5</v>
       </c>
       <c r="M11" s="1">
-        <f>ROUNDDOWN(L11*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N11" s="10">
         <v>7637627</v>
       </c>
       <c r="O11" s="7">
-        <f>N11/K11</f>
+        <f t="shared" si="5"/>
         <v>8430.0518763796917</v>
       </c>
       <c r="P11" s="7">
-        <f>M11*O11</f>
+        <f t="shared" si="6"/>
         <v>33720.207505518767</v>
       </c>
     </row>
@@ -15405,40 +15405,40 @@
         <v>4.0823974880830798E-6</v>
       </c>
       <c r="G12" s="1">
-        <f>ROUNDDOWN(F12*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H12" s="10">
         <v>793</v>
       </c>
       <c r="I12" s="7">
-        <f>H12/E12</f>
+        <f t="shared" si="1"/>
         <v>4.9254658385093171</v>
       </c>
       <c r="J12" s="7">
-        <f>I12*G12</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12" s="1">
         <v>46</v>
       </c>
       <c r="L12" s="3">
-        <f>K12/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.1663992823094503E-6</v>
       </c>
       <c r="M12" s="1">
-        <f>ROUNDDOWN(L12*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N12" s="10">
         <v>200</v>
       </c>
       <c r="O12" s="7">
-        <f>N12/K12</f>
+        <f t="shared" si="5"/>
         <v>4.3478260869565215</v>
       </c>
       <c r="P12" s="7">
-        <f>M12*O12</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -15459,40 +15459,40 @@
         <v>5.9587789422330599E-6</v>
       </c>
       <c r="G13" s="1">
-        <f>ROUNDDOWN(F13*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H13" s="10">
         <v>6064748</v>
       </c>
       <c r="I13" s="7">
-        <f>H13/E13</f>
+        <f t="shared" si="1"/>
         <v>25807.438297872341</v>
       </c>
       <c r="J13" s="7">
-        <f>I13*G13</f>
+        <f t="shared" si="2"/>
         <v>25807.438297872341</v>
       </c>
       <c r="K13" s="1">
         <v>71</v>
       </c>
       <c r="L13" s="3">
-        <f>K13/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.8003119357384994E-6</v>
       </c>
       <c r="M13" s="1">
-        <f>ROUNDDOWN(L13*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N13" s="10">
         <v>3326746</v>
       </c>
       <c r="O13" s="7">
-        <f>N13/K13</f>
+        <f t="shared" si="5"/>
         <v>46855.57746478873</v>
       </c>
       <c r="P13" s="7">
-        <f>M13*O13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -15513,40 +15513,40 @@
         <v>5.0281951669992202E-5</v>
       </c>
       <c r="G14" s="1">
-        <f>ROUNDDOWN(F14*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H14" s="10">
         <v>6440960</v>
       </c>
       <c r="I14" s="7">
-        <f>H14/E14</f>
+        <f t="shared" si="1"/>
         <v>3248.0887544125062</v>
       </c>
       <c r="J14" s="7">
-        <f>I14*G14</f>
+        <f t="shared" si="2"/>
         <v>29232.798789712557</v>
       </c>
       <c r="K14" s="1">
         <v>983</v>
       </c>
       <c r="L14" s="3">
-        <f>K14/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.4925445532830209E-5</v>
       </c>
       <c r="M14" s="1">
-        <f>ROUNDDOWN(L14*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N14" s="10">
         <v>4485530</v>
       </c>
       <c r="O14" s="7">
-        <f>N14/K14</f>
+        <f t="shared" si="5"/>
         <v>4563.1027466937949</v>
       </c>
       <c r="P14" s="7">
-        <f>M14*O14</f>
+        <f t="shared" si="6"/>
         <v>18252.410986775179</v>
       </c>
     </row>
@@ -15567,40 +15567,40 @@
         <v>1.6765721857891499E-4</v>
       </c>
       <c r="G15" s="1">
-        <f>ROUNDDOWN(F15*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H15" s="11">
         <v>26675566</v>
       </c>
-      <c r="I15" s="19">
-        <f>H15/E15</f>
+      <c r="I15" s="18">
+        <f t="shared" si="1"/>
         <v>4034.4171203871747</v>
       </c>
       <c r="J15" s="7">
-        <f>I15*G15</f>
+        <f t="shared" si="2"/>
         <v>121032.51361161524</v>
       </c>
       <c r="K15" s="1">
         <v>783</v>
       </c>
       <c r="L15" s="3">
-        <f>K15/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.9854144305397818E-5</v>
       </c>
       <c r="M15" s="1">
-        <f>ROUNDDOWN(L15*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N15" s="10">
         <v>3572557</v>
       </c>
       <c r="O15" s="7">
-        <f>N15/K15</f>
+        <f t="shared" si="5"/>
         <v>4562.6526181353765</v>
       </c>
       <c r="P15" s="7">
-        <f>M15*O15</f>
+        <f t="shared" si="6"/>
         <v>13687.95785440613</v>
       </c>
     </row>
@@ -15621,40 +15621,40 @@
         <v>4.88873438324483E-5</v>
       </c>
       <c r="G16" s="1">
-        <f>ROUNDDOWN(F16*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="H16" s="10">
         <v>29053752</v>
       </c>
       <c r="I16" s="7">
-        <f>H16/E16</f>
+        <f t="shared" si="1"/>
         <v>15069.373443983402</v>
       </c>
       <c r="J16" s="7">
-        <f>I16*G16</f>
+        <f t="shared" si="2"/>
         <v>120554.98755186722</v>
       </c>
       <c r="K16" s="1">
         <v>300</v>
       </c>
       <c r="L16" s="3">
-        <f>K16/$E$5</f>
+        <f t="shared" si="3"/>
         <v>7.6069518411485885E-6</v>
       </c>
       <c r="M16" s="1">
-        <f>ROUNDDOWN(L16*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N16" s="10">
         <v>6622540</v>
       </c>
       <c r="O16" s="7">
-        <f>N16/K16</f>
+        <f t="shared" si="5"/>
         <v>22075.133333333335</v>
       </c>
       <c r="P16" s="7">
-        <f>M16*O16</f>
+        <f t="shared" si="6"/>
         <v>22075.133333333335</v>
       </c>
     </row>
@@ -15673,34 +15673,34 @@
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <f>ROUNDDOWN(F17*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="7" t="e">
-        <f>H17/E17</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="7" t="e">
-        <f>I17*G17</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="3">
-        <f>K17/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f>ROUNDDOWN(L17*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="7" t="e">
-        <f>N17/K17</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="7" t="e">
-        <f>M17*O17</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15721,40 +15721,40 @@
         <v>9.9397504057674903E-6</v>
       </c>
       <c r="G18" s="1">
-        <f>ROUNDDOWN(F18*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H18" s="10">
         <v>3617279</v>
       </c>
       <c r="I18" s="7">
-        <f>H18/E18</f>
+        <f t="shared" si="1"/>
         <v>9227.7525510204086</v>
       </c>
       <c r="J18" s="7">
-        <f>I18*G18</f>
+        <f t="shared" si="2"/>
         <v>9227.7525510204086</v>
       </c>
       <c r="K18" s="1">
         <v>199</v>
       </c>
       <c r="L18" s="3">
-        <f>K18/$E$5</f>
+        <f t="shared" si="3"/>
         <v>5.045944721295231E-6</v>
       </c>
       <c r="M18" s="1">
-        <f>ROUNDDOWN(L18*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N18" s="10">
         <v>2398648</v>
       </c>
       <c r="O18" s="7">
-        <f>N18/K18</f>
+        <f t="shared" si="5"/>
         <v>12053.507537688442</v>
       </c>
       <c r="P18" s="7">
-        <f>M18*O18</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -15775,40 +15775,40 @@
         <v>4.9115552387682701E-5</v>
       </c>
       <c r="G19" s="1">
-        <f>ROUNDDOWN(F19*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="H19" s="10">
         <v>32127429</v>
       </c>
       <c r="I19" s="7">
-        <f>H19/E19</f>
+        <f t="shared" si="1"/>
         <v>16586.179143004647</v>
       </c>
       <c r="J19" s="7">
-        <f>I19*G19</f>
+        <f t="shared" si="2"/>
         <v>132689.43314403718</v>
       </c>
       <c r="K19" s="1">
         <v>699</v>
       </c>
       <c r="L19" s="3">
-        <f>K19/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.7724197789876212E-5</v>
       </c>
       <c r="M19" s="1">
-        <f>ROUNDDOWN(L19*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N19" s="10">
         <v>11709827</v>
       </c>
       <c r="O19" s="7">
-        <f>N19/K19</f>
+        <f t="shared" si="5"/>
         <v>16752.25608011445</v>
       </c>
       <c r="P19" s="7">
-        <f>M19*O19</f>
+        <f t="shared" si="6"/>
         <v>50256.76824034335</v>
       </c>
     </row>
@@ -15829,38 +15829,38 @@
         <v>1.0142602454864799E-5</v>
       </c>
       <c r="G20" s="1">
-        <f>ROUNDDOWN(F20*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="7">
-        <f>H20/E20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="7">
-        <f>I20*G20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>318</v>
       </c>
       <c r="L20" s="3">
-        <f>K20/$E$5</f>
+        <f t="shared" si="3"/>
         <v>8.0633689516175034E-6</v>
       </c>
       <c r="M20" s="1">
-        <f>ROUNDDOWN(L20*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N20" s="10">
         <v>21721653</v>
       </c>
       <c r="O20" s="7">
-        <f>N20/K20</f>
+        <f t="shared" si="5"/>
         <v>68307.084905660377</v>
       </c>
       <c r="P20" s="7">
-        <f>M20*O20</f>
+        <f t="shared" si="6"/>
         <v>68307.084905660377</v>
       </c>
     </row>
@@ -15881,38 +15881,38 @@
         <v>1.5036408139337E-5</v>
       </c>
       <c r="G21" s="1">
-        <f>ROUNDDOWN(F21*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H21" s="10">
         <v>7871344</v>
       </c>
       <c r="I21" s="7">
-        <f>H21/E21</f>
+        <f t="shared" si="1"/>
         <v>13273.767284991569</v>
       </c>
       <c r="J21" s="7">
-        <f>I21*G21</f>
+        <f t="shared" si="2"/>
         <v>26547.534569983138</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="3">
-        <f>K21/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <f>ROUNDDOWN(L21*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N21" s="10">
         <v>2190447</v>
       </c>
       <c r="O21" s="7" t="e">
-        <f>N21/K21</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="7" t="e">
-        <f>M21*O21</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15933,38 +15933,38 @@
         <v>6.8716131631708897E-6</v>
       </c>
       <c r="G22" s="1">
-        <f>ROUNDDOWN(F22*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H22" s="10">
         <v>215843</v>
       </c>
       <c r="I22" s="7">
-        <f>H22/E22</f>
+        <f t="shared" si="1"/>
         <v>796.46863468634683</v>
       </c>
       <c r="J22" s="7">
-        <f>I22*G22</f>
+        <f t="shared" si="2"/>
         <v>796.46863468634683</v>
       </c>
       <c r="K22" s="1">
         <v>60</v>
       </c>
       <c r="L22" s="3">
-        <f>K22/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.5213903682297178E-6</v>
       </c>
       <c r="M22" s="1">
-        <f>ROUNDDOWN(L22*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N22" s="10"/>
       <c r="O22" s="7">
-        <f>N22/K22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P22" s="7">
-        <f>M22*O22</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -15983,34 +15983,34 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <f>ROUNDDOWN(F23*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="7" t="e">
-        <f>H23/E23</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f>I23*G23</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="3">
-        <f>K23/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f>ROUNDDOWN(L23*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="7" t="e">
-        <f>N23/K23</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="7" t="e">
-        <f>M23*O23</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -16029,34 +16029,34 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <f>ROUNDDOWN(F24*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="7" t="e">
-        <f>H24/E24</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f>I24*G24</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="3">
-        <f>K24/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>ROUNDDOWN(L24*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="7" t="e">
-        <f>N24/K24</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="7" t="e">
-        <f>M24*O24</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -16077,40 +16077,40 @@
         <v>1.3885222760709901E-4</v>
       </c>
       <c r="G25" s="1">
-        <f>ROUNDDOWN(F25*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
       </c>
       <c r="I25" s="7">
-        <f>H25/E25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="7">
-        <f>I25*G25</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K25" s="1">
         <v>1743</v>
       </c>
       <c r="L25" s="3">
-        <f>K25/$E$5</f>
+        <f t="shared" si="3"/>
         <v>4.4196390197073303E-5</v>
       </c>
       <c r="M25" s="1">
-        <f>ROUNDDOWN(L25*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="N25" s="10">
         <v>0</v>
       </c>
       <c r="O25" s="7">
-        <f>N25/K25</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P25" s="7">
-        <f>M25*O25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -16131,40 +16131,40 @@
         <v>2.0330846620776499E-4</v>
       </c>
       <c r="G26" s="1">
-        <f>ROUNDDOWN(F26*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="H26" s="10">
         <v>26755670</v>
       </c>
       <c r="I26" s="7">
-        <f>H26/E26</f>
+        <f t="shared" si="1"/>
         <v>3336.9506111249689</v>
       </c>
       <c r="J26" s="7">
-        <f>I26*G26</f>
+        <f t="shared" si="2"/>
         <v>123467.17261162384</v>
       </c>
       <c r="K26" s="1">
         <v>4074</v>
       </c>
       <c r="L26" s="3">
-        <f>K26/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.0330240600279784E-4</v>
       </c>
       <c r="M26" s="1">
-        <f>ROUNDDOWN(L26*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="N26" s="10">
         <v>27009645</v>
       </c>
       <c r="O26" s="7">
-        <f>N26/K26</f>
+        <f t="shared" si="5"/>
         <v>6629.7606774668629</v>
       </c>
       <c r="P26" s="7">
-        <f>M26*O26</f>
+        <f t="shared" si="6"/>
         <v>119335.69219440353</v>
       </c>
     </row>
@@ -16185,40 +16185,40 @@
         <v>5.5429322415836001E-5</v>
       </c>
       <c r="G27" s="1">
-        <f>ROUNDDOWN(F27*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H27" s="10">
         <v>5480991</v>
       </c>
       <c r="I27" s="7">
-        <f>H27/E27</f>
+        <f t="shared" si="1"/>
         <v>2507.3151875571821</v>
       </c>
       <c r="J27" s="7">
-        <f>I27*G27</f>
+        <f t="shared" si="2"/>
         <v>25073.151875571821</v>
       </c>
       <c r="K27" s="1">
         <v>691</v>
       </c>
       <c r="L27" s="3">
-        <f>K27/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.7521345740778916E-5</v>
       </c>
       <c r="M27" s="1">
-        <f>ROUNDDOWN(L27*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N27" s="10">
         <v>1821853</v>
       </c>
       <c r="O27" s="7">
-        <f>N27/K27</f>
+        <f t="shared" si="5"/>
         <v>2636.5455861070914</v>
       </c>
       <c r="P27" s="7">
-        <f>M27*O27</f>
+        <f t="shared" si="6"/>
         <v>7909.6367583212741</v>
       </c>
     </row>
@@ -16239,40 +16239,40 @@
         <v>5.8953876768901597E-5</v>
       </c>
       <c r="G28" s="1">
-        <f>ROUNDDOWN(F28*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H28" s="10">
         <v>9715527</v>
       </c>
       <c r="I28" s="7">
-        <f>H28/E28</f>
+        <f t="shared" si="1"/>
         <v>4178.7212903225809</v>
       </c>
       <c r="J28" s="7">
-        <f>I28*G28</f>
+        <f t="shared" si="2"/>
         <v>41787.212903225809</v>
       </c>
       <c r="K28" s="1">
         <v>1057</v>
       </c>
       <c r="L28" s="3">
-        <f>K28/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.6801826986980194E-5</v>
       </c>
       <c r="M28" s="1">
-        <f>ROUNDDOWN(L28*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N28" s="10">
         <v>5440103</v>
       </c>
       <c r="O28" s="7">
-        <f>N28/K28</f>
+        <f t="shared" si="5"/>
         <v>5146.7388836329237</v>
       </c>
       <c r="P28" s="7">
-        <f>M28*O28</f>
+        <f t="shared" si="6"/>
         <v>20586.955534531695</v>
       </c>
     </row>
@@ -16293,40 +16293,40 @@
         <v>1.3634193349952001E-4</v>
       </c>
       <c r="G29" s="1">
-        <f>ROUNDDOWN(F29*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="H29" s="10">
         <v>17672566</v>
       </c>
       <c r="I29" s="7">
-        <f>H29/E29</f>
+        <f t="shared" si="1"/>
         <v>3286.6962990515158</v>
       </c>
       <c r="J29" s="7">
-        <f>I29*G29</f>
+        <f t="shared" si="2"/>
         <v>78880.711177236371</v>
       </c>
       <c r="K29" s="1">
         <v>1711</v>
       </c>
       <c r="L29" s="3">
-        <f>K29/$E$5</f>
+        <f t="shared" si="3"/>
         <v>4.3384982000684121E-5</v>
       </c>
       <c r="M29" s="1">
-        <f>ROUNDDOWN(L29*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="N29" s="10">
         <v>7700878</v>
       </c>
       <c r="O29" s="7">
-        <f>N29/K29</f>
+        <f t="shared" si="5"/>
         <v>4500.8053769725311</v>
       </c>
       <c r="P29" s="7">
-        <f>M29*O29</f>
+        <f t="shared" si="6"/>
         <v>31505.637638807719</v>
       </c>
     </row>
@@ -16347,40 +16347,40 @@
         <v>6.8640062113297395E-5</v>
       </c>
       <c r="G30" s="1">
-        <f>ROUNDDOWN(F30*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="H30" s="10">
         <v>6005044</v>
       </c>
       <c r="I30" s="7">
-        <f>H30/E30</f>
+        <f t="shared" si="1"/>
         <v>2218.3391207979312</v>
       </c>
       <c r="J30" s="7">
-        <f>I30*G30</f>
+        <f t="shared" si="2"/>
         <v>26620.069449575174</v>
       </c>
       <c r="K30" s="1">
         <v>750</v>
       </c>
       <c r="L30" s="3">
-        <f>K30/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.9017379602871473E-5</v>
       </c>
       <c r="M30" s="1">
-        <f>ROUNDDOWN(L30*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N30" s="10">
         <v>2345166</v>
       </c>
       <c r="O30" s="7">
-        <f>N30/K30</f>
+        <f t="shared" si="5"/>
         <v>3126.8879999999999</v>
       </c>
       <c r="P30" s="7">
-        <f>M30*O30</f>
+        <f t="shared" si="6"/>
         <v>9380.6640000000007</v>
       </c>
     </row>
@@ -16401,40 +16401,40 @@
         <v>7.6830213595600803E-6</v>
       </c>
       <c r="G31" s="1">
-        <f>ROUNDDOWN(F31*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H31" s="10">
         <v>1448357</v>
       </c>
       <c r="I31" s="7">
-        <f>H31/E31</f>
+        <f t="shared" si="1"/>
         <v>4780.0561056105607</v>
       </c>
       <c r="J31" s="7">
-        <f>I31*G31</f>
+        <f t="shared" si="2"/>
         <v>4780.0561056105607</v>
       </c>
       <c r="K31" s="1">
         <v>25</v>
       </c>
       <c r="L31" s="3">
-        <f>K31/$E$5</f>
+        <f t="shared" si="3"/>
         <v>6.3391265342904911E-7</v>
       </c>
       <c r="M31" s="1">
-        <f>ROUNDDOWN(L31*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N31" s="10">
         <v>76345</v>
       </c>
       <c r="O31" s="7">
-        <f>N31/K31</f>
+        <f t="shared" si="5"/>
         <v>3053.8</v>
       </c>
       <c r="P31" s="7">
-        <f>M31*O31</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -16455,40 +16455,40 @@
         <v>6.0247058581896801E-5</v>
       </c>
       <c r="G32" s="1">
-        <f>ROUNDDOWN(F32*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="H32" s="10">
         <v>56285319</v>
       </c>
       <c r="I32" s="7">
-        <f>H32/E32</f>
+        <f t="shared" si="1"/>
         <v>23689.107323232322</v>
       </c>
       <c r="J32" s="7">
-        <f>I32*G32</f>
+        <f t="shared" si="2"/>
         <v>260580.18055555553</v>
       </c>
       <c r="K32" s="1">
         <v>909</v>
       </c>
       <c r="L32" s="3">
-        <f>K32/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.3049064078680224E-5</v>
       </c>
       <c r="M32" s="1">
-        <f>ROUNDDOWN(L32*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N32" s="10">
         <v>9413584</v>
       </c>
       <c r="O32" s="7">
-        <f>N32/K32</f>
+        <f t="shared" si="5"/>
         <v>10355.97799779978</v>
       </c>
       <c r="P32" s="7">
-        <f>M32*O32</f>
+        <f t="shared" si="6"/>
         <v>41423.911991199122</v>
       </c>
     </row>
@@ -16507,34 +16507,34 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <f>ROUNDDOWN(F33*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="7" t="e">
-        <f>H33/E33</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="7" t="e">
-        <f>I33*G33</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="3">
-        <f>K33/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f>ROUNDDOWN(L33*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="7" t="e">
-        <f>N33/K33</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="7" t="e">
-        <f>M33*O33</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -16555,40 +16555,40 @@
         <v>7.3280302736398101E-5</v>
       </c>
       <c r="G34" s="1">
-        <f>ROUNDDOWN(F34*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="H34" s="10">
         <v>58875334</v>
       </c>
       <c r="I34" s="7">
-        <f>H34/E34</f>
+        <f t="shared" si="1"/>
         <v>20372.087889273356</v>
       </c>
       <c r="J34" s="7">
-        <f>I34*G34</f>
+        <f t="shared" si="2"/>
         <v>264837.14256055362</v>
       </c>
       <c r="K34" s="1">
         <v>802</v>
       </c>
       <c r="L34" s="3">
-        <f>K34/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.0335917922003894E-5</v>
       </c>
       <c r="M34" s="1">
-        <f>ROUNDDOWN(L34*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N34" s="10">
         <v>12050817</v>
       </c>
       <c r="O34" s="7">
-        <f>N34/K34</f>
+        <f t="shared" si="5"/>
         <v>15025.956359102245</v>
       </c>
       <c r="P34" s="7">
-        <f>M34*O34</f>
+        <f t="shared" si="6"/>
         <v>45077.869077306736</v>
       </c>
     </row>
@@ -16609,40 +16609,40 @@
         <v>4.5007798393462499E-5</v>
       </c>
       <c r="G35" s="1">
-        <f>ROUNDDOWN(F35*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="H35" s="10">
         <v>7706581</v>
       </c>
       <c r="I35" s="7">
-        <f>H35/E35</f>
+        <f t="shared" si="1"/>
         <v>4341.7357746478874</v>
       </c>
       <c r="J35" s="7">
-        <f>I35*G35</f>
+        <f t="shared" si="2"/>
         <v>34733.886197183099</v>
       </c>
       <c r="K35" s="1">
         <v>856</v>
       </c>
       <c r="L35" s="3">
-        <f>K35/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.170516925341064E-5</v>
       </c>
       <c r="M35" s="1">
-        <f>ROUNDDOWN(L35*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N35" s="10">
         <v>6511664</v>
       </c>
       <c r="O35" s="7">
-        <f>N35/K35</f>
+        <f t="shared" si="5"/>
         <v>7607.0841121495323</v>
       </c>
       <c r="P35" s="7">
-        <f>M35*O35</f>
+        <f t="shared" si="6"/>
         <v>22821.252336448597</v>
       </c>
     </row>
@@ -16663,46 +16663,46 @@
         <v>5.5125044342190101E-5</v>
       </c>
       <c r="G36" s="1">
-        <f>ROUNDDOWN(F36*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H36" s="10">
         <v>2703704</v>
       </c>
       <c r="I36" s="7">
-        <f>H36/E36</f>
+        <f t="shared" si="1"/>
         <v>1243.6540938362466</v>
       </c>
       <c r="J36" s="7">
-        <f>I36*G36</f>
+        <f t="shared" si="2"/>
         <v>12436.540938362466</v>
       </c>
       <c r="K36" s="1">
         <v>954</v>
       </c>
       <c r="L36" s="3">
-        <f>K36/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.4190106854852512E-5</v>
       </c>
       <c r="M36" s="1">
-        <f>ROUNDDOWN(L36*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N36" s="11">
         <v>1180858</v>
       </c>
       <c r="O36" s="7">
-        <f>N36/K36</f>
+        <f t="shared" si="5"/>
         <v>1237.796645702306</v>
       </c>
       <c r="P36" s="7">
-        <f>M36*O36</f>
+        <f t="shared" si="6"/>
         <v>4951.1865828092241</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="J37" s="7">
-        <f t="shared" ref="J8:J38" si="0">I37*G37</f>
+        <f t="shared" ref="J37:J38" si="7">I37*G37</f>
         <v>0</v>
       </c>
       <c r="L37" s="3"/>
@@ -16716,11 +16716,11 @@
         <v>59375</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" ref="I9:I38" si="1">H38/E38</f>
+        <f t="shared" ref="I38" si="8">H38/E38</f>
         <v>0</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L38" s="3"/>
@@ -16881,40 +16881,40 @@
         <v>3.7862096129105203E-5</v>
       </c>
       <c r="G7" s="1">
-        <f>ROUNDDOWN(F7*$E$6,0)</f>
+        <f t="shared" ref="G7:G36" si="0">ROUNDDOWN(F7*$E$6,0)</f>
         <v>6</v>
       </c>
       <c r="H7" s="10">
         <v>19531058</v>
       </c>
       <c r="I7" s="7">
-        <f>H7/E7</f>
+        <f t="shared" ref="I7:I36" si="1">H7/E7</f>
         <v>13046.798931195724</v>
       </c>
       <c r="J7" s="7">
-        <f>I7*G7</f>
+        <f t="shared" ref="J7:J36" si="2">I7*G7</f>
         <v>78280.793587174354</v>
       </c>
       <c r="K7" s="1">
         <v>778</v>
       </c>
       <c r="L7" s="3">
-        <f>K7/$E$5</f>
+        <f t="shared" ref="L7:L36" si="3">K7/$E$5</f>
         <v>1.9677161515326573E-5</v>
       </c>
       <c r="M7" s="1">
-        <f>ROUNDDOWN(L7*$E$6,0)</f>
+        <f t="shared" ref="M7:M36" si="4">ROUNDDOWN(L7*$E$6,0)</f>
         <v>3</v>
       </c>
       <c r="N7" s="10">
         <v>8991086</v>
       </c>
       <c r="O7" s="7">
-        <f>N7/K7</f>
+        <f t="shared" ref="O7:O36" si="5">N7/K7</f>
         <v>11556.665809768638</v>
       </c>
       <c r="P7" s="7">
-        <f>M7*O7</f>
+        <f t="shared" ref="P7:P36" si="6">M7*O7</f>
         <v>34669.997429305913</v>
       </c>
     </row>
@@ -16935,38 +16935,38 @@
         <v>7.3953753561458704E-5</v>
       </c>
       <c r="G8" s="1">
-        <f>ROUNDDOWN(F8*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="7">
-        <f>H8/E8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="7">
-        <f>I8*G8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>428</v>
       </c>
       <c r="L8" s="3">
-        <f>K8/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.0824968031567832E-5</v>
       </c>
       <c r="M8" s="1">
-        <f>ROUNDDOWN(L8*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N8" s="10">
         <v>31866447</v>
       </c>
       <c r="O8" s="7">
-        <f>N8/K8</f>
+        <f t="shared" si="5"/>
         <v>74454.315420560742</v>
       </c>
       <c r="P8" s="7">
-        <f>M8*O8</f>
+        <f t="shared" si="6"/>
         <v>74454.315420560742</v>
       </c>
     </row>
@@ -16985,34 +16985,34 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <f>ROUNDDOWN(F9*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="7" t="e">
-        <f>H9/E9</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="7" t="e">
-        <f>I9*G9</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="3">
-        <f>K9/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f>ROUNDDOWN(L9*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="7" t="e">
-        <f>N9/K9</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="7" t="e">
-        <f>M9*O9</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17033,40 +17033,40 @@
         <v>7.8658062098541998E-5</v>
       </c>
       <c r="G10" s="1">
-        <f>ROUNDDOWN(F10*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="H10" s="10">
         <v>120492182</v>
       </c>
       <c r="I10" s="7">
-        <f>H10/E10</f>
+        <f t="shared" si="1"/>
         <v>38743.466881028937</v>
       </c>
       <c r="J10" s="7">
-        <f>I10*G10</f>
+        <f t="shared" si="2"/>
         <v>542408.53633440507</v>
       </c>
       <c r="K10" s="1">
         <v>1384</v>
       </c>
       <c r="L10" s="3">
-        <f>K10/$E$5</f>
+        <f t="shared" si="3"/>
         <v>3.5004102232920282E-5</v>
       </c>
       <c r="M10" s="1">
-        <f>ROUNDDOWN(L10*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="N10" s="10">
         <v>69686021</v>
       </c>
       <c r="O10" s="7">
-        <f>N10/K10</f>
+        <f t="shared" si="5"/>
         <v>50351.171242774566</v>
       </c>
       <c r="P10" s="7">
-        <f>M10*O10</f>
+        <f t="shared" si="6"/>
         <v>302107.02745664737</v>
       </c>
     </row>
@@ -17087,40 +17087,40 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <f>ROUNDDOWN(F11*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H11" s="11">
         <v>15484731</v>
       </c>
       <c r="I11" s="7">
-        <f>H11/E11</f>
+        <f t="shared" si="1"/>
         <v>5872.1012514220702</v>
       </c>
       <c r="J11" s="7">
-        <f>I11*G11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="1">
         <v>1128</v>
       </c>
       <c r="L11" s="3">
-        <f>K11/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.8529354999085315E-5</v>
       </c>
       <c r="M11" s="1">
-        <f>ROUNDDOWN(L11*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="N11" s="10">
         <v>9640764</v>
       </c>
       <c r="O11" s="7">
-        <f>N11/K11</f>
+        <f t="shared" si="5"/>
         <v>8546.7765957446809</v>
       </c>
       <c r="P11" s="7">
-        <f>M11*O11</f>
+        <f t="shared" si="6"/>
         <v>42733.882978723406</v>
       </c>
     </row>
@@ -17141,40 +17141,40 @@
         <v>1.0319128403924501E-5</v>
       </c>
       <c r="G12" s="1">
-        <f>ROUNDDOWN(F12*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H12" s="10">
         <v>434348</v>
       </c>
       <c r="I12" s="7">
-        <f>H12/E12</f>
+        <f t="shared" si="1"/>
         <v>1064.5784313725489</v>
       </c>
       <c r="J12" s="7">
-        <f>I12*G12</f>
+        <f t="shared" si="2"/>
         <v>1064.5784313725489</v>
       </c>
       <c r="K12" s="1">
         <v>85</v>
       </c>
       <c r="L12" s="3">
-        <f>K12/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.1498184174842656E-6</v>
       </c>
       <c r="M12" s="1">
-        <f>ROUNDDOWN(L12*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N12" s="10">
         <v>11989</v>
       </c>
       <c r="O12" s="7">
-        <f>N12/K12</f>
+        <f t="shared" si="5"/>
         <v>141.04705882352943</v>
       </c>
       <c r="P12" s="7">
-        <f>M12*O12</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -17195,40 +17195,40 @@
         <v>9.2821571672555896E-6</v>
       </c>
       <c r="G13" s="1">
-        <f>ROUNDDOWN(F13*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H13" s="10">
         <v>26713249</v>
       </c>
       <c r="I13" s="7">
-        <f>H13/E13</f>
+        <f t="shared" si="1"/>
         <v>72788.144414168943</v>
       </c>
       <c r="J13" s="7">
-        <f>I13*G13</f>
+        <f t="shared" si="2"/>
         <v>72788.144414168943</v>
       </c>
       <c r="K13" s="1">
         <v>96</v>
       </c>
       <c r="L13" s="3">
-        <f>K13/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.428030212688112E-6</v>
       </c>
       <c r="M13" s="1">
-        <f>ROUNDDOWN(L13*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N13" s="10">
         <v>5226532</v>
       </c>
       <c r="O13" s="7">
-        <f>N13/K13</f>
+        <f t="shared" si="5"/>
         <v>54443.041666666664</v>
       </c>
       <c r="P13" s="7">
-        <f>M13*O13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -17249,40 +17249,40 @@
         <v>5.9562616155005201E-5</v>
       </c>
       <c r="G14" s="1">
-        <f>ROUNDDOWN(F14*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H14" s="10">
         <v>12826945</v>
       </c>
       <c r="I14" s="7">
-        <f>H14/E14</f>
+        <f t="shared" si="1"/>
         <v>5446.6857749469218</v>
       </c>
       <c r="J14" s="7">
-        <f>I14*G14</f>
+        <f t="shared" si="2"/>
         <v>54466.857749469214</v>
       </c>
       <c r="K14" s="1">
         <v>1067</v>
       </c>
       <c r="L14" s="3">
-        <f>K14/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.6986544134773076E-5</v>
       </c>
       <c r="M14" s="1">
-        <f>ROUNDDOWN(L14*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N14" s="10">
         <v>7805888</v>
       </c>
       <c r="O14" s="7">
-        <f>N14/K14</f>
+        <f t="shared" si="5"/>
         <v>7315.7338331771325</v>
       </c>
       <c r="P14" s="7">
-        <f>M14*O14</f>
+        <f t="shared" si="6"/>
         <v>29262.93533270853</v>
       </c>
     </row>
@@ -17303,40 +17303,40 @@
         <v>2.8046278154685901E-4</v>
       </c>
       <c r="G15" s="1">
-        <f>ROUNDDOWN(F15*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="H15" s="10">
         <v>16283934</v>
       </c>
       <c r="I15" s="7">
-        <f>H15/E15</f>
+        <f t="shared" si="1"/>
         <v>1468.4763278925061</v>
       </c>
       <c r="J15" s="7">
-        <f>I15*G15</f>
+        <f t="shared" si="2"/>
         <v>73423.816394625304</v>
       </c>
       <c r="K15" s="1">
         <v>1154</v>
       </c>
       <c r="L15" s="3">
-        <f>K15/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.9186946515021679E-5</v>
       </c>
       <c r="M15" s="1">
-        <f>ROUNDDOWN(L15*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="N15" s="10">
         <v>3408726</v>
       </c>
       <c r="O15" s="7">
-        <f>N15/K15</f>
+        <f t="shared" si="5"/>
         <v>2953.8353552859617</v>
       </c>
       <c r="P15" s="7">
-        <f>M15*O15</f>
+        <f t="shared" si="6"/>
         <v>14769.176776429809</v>
       </c>
     </row>
@@ -17357,40 +17357,40 @@
         <v>3.6395161208939501E-5</v>
       </c>
       <c r="G16" s="1">
-        <f>ROUNDDOWN(F16*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H16" s="10">
         <v>28344200</v>
       </c>
       <c r="I16" s="7">
-        <f>H16/E16</f>
+        <f t="shared" si="1"/>
         <v>19697.150799166087</v>
       </c>
       <c r="J16" s="7">
-        <f>I16*G16</f>
+        <f t="shared" si="2"/>
         <v>118182.90479499652</v>
       </c>
       <c r="K16" s="1">
         <v>296</v>
       </c>
       <c r="L16" s="3">
-        <f>K16/$E$5</f>
+        <f t="shared" si="3"/>
         <v>7.4864264891216787E-6</v>
       </c>
       <c r="M16" s="1">
-        <f>ROUNDDOWN(L16*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N16" s="10">
         <v>3835156</v>
       </c>
       <c r="O16" s="7">
-        <f>N16/K16</f>
+        <f t="shared" si="5"/>
         <v>12956.608108108108</v>
       </c>
       <c r="P16" s="7">
-        <f>M16*O16</f>
+        <f t="shared" si="6"/>
         <v>12956.608108108108</v>
       </c>
     </row>
@@ -17409,34 +17409,34 @@
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <f>ROUNDDOWN(F17*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="7" t="e">
-        <f>H17/E17</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="7" t="e">
-        <f>I17*G17</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="3">
-        <f>K17/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f>ROUNDDOWN(L17*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="7" t="e">
-        <f>N17/K17</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="7" t="e">
-        <f>M17*O17</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17457,40 +17457,40 @@
         <v>1.26712826724661E-5</v>
       </c>
       <c r="G18" s="1">
-        <f>ROUNDDOWN(F18*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H18" s="10">
         <v>1669155</v>
       </c>
       <c r="I18" s="7">
-        <f>H18/E18</f>
+        <f t="shared" si="1"/>
         <v>3331.6467065868264</v>
       </c>
       <c r="J18" s="7">
-        <f>I18*G18</f>
+        <f t="shared" si="2"/>
         <v>6663.2934131736529</v>
       </c>
       <c r="K18" s="1">
         <v>226</v>
       </c>
       <c r="L18" s="3">
-        <f>K18/$E$5</f>
+        <f t="shared" si="3"/>
         <v>5.7159877923699304E-6</v>
       </c>
       <c r="M18" s="1">
-        <f>ROUNDDOWN(L18*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N18" s="10">
         <v>1560816</v>
       </c>
       <c r="O18" s="7">
-        <f>N18/K18</f>
+        <f t="shared" si="5"/>
         <v>6906.2654867256633</v>
       </c>
       <c r="P18" s="7">
-        <f>M18*O18</f>
+        <f t="shared" si="6"/>
         <v>6906.2654867256633</v>
       </c>
     </row>
@@ -17511,40 +17511,40 @@
         <v>8.5233977257905596E-5</v>
       </c>
       <c r="G19" s="1">
-        <f>ROUNDDOWN(F19*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="H19" s="10">
         <v>23011137</v>
       </c>
       <c r="I19" s="7">
-        <f>H19/E19</f>
+        <f t="shared" si="1"/>
         <v>6828.2305637982199</v>
       </c>
       <c r="J19" s="7">
-        <f>I19*G19</f>
+        <f t="shared" si="2"/>
         <v>102423.4584569733</v>
       </c>
       <c r="K19" s="1">
         <v>1112</v>
       </c>
       <c r="L19" s="3">
-        <f>K19/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.8124683296970631E-5</v>
       </c>
       <c r="M19" s="1">
-        <f>ROUNDDOWN(L19*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="N19" s="10">
         <v>9552167</v>
       </c>
       <c r="O19" s="7">
-        <f>N19/K19</f>
+        <f t="shared" si="5"/>
         <v>8590.0782374100727</v>
       </c>
       <c r="P19" s="7">
-        <f>M19*O19</f>
+        <f t="shared" si="6"/>
         <v>42950.391187050365</v>
       </c>
     </row>
@@ -17565,38 +17565,38 @@
         <v>2.5949572898104199E-5</v>
       </c>
       <c r="G20" s="1">
-        <f>ROUNDDOWN(F20*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="7">
-        <f>H20/E20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="7">
-        <f>I20*G20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>762</v>
       </c>
       <c r="L20" s="3">
-        <f>K20/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.9272489813211889E-5</v>
       </c>
       <c r="M20" s="1">
-        <f>ROUNDDOWN(L20*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N20" s="10">
         <v>36608176</v>
       </c>
       <c r="O20" s="7">
-        <f>N20/K20</f>
+        <f t="shared" si="5"/>
         <v>48042.22572178478</v>
       </c>
       <c r="P20" s="7">
-        <f>M20*O20</f>
+        <f t="shared" si="6"/>
         <v>144126.67716535434</v>
       </c>
     </row>
@@ -17617,38 +17617,38 @@
         <v>1.83366865020717E-5</v>
       </c>
       <c r="G21" s="1">
-        <f>ROUNDDOWN(F21*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H21" s="10">
         <v>13169635</v>
       </c>
       <c r="I21" s="7">
-        <f>H21/E21</f>
+        <f t="shared" si="1"/>
         <v>18165.013793103448</v>
       </c>
       <c r="J21" s="7">
-        <f>I21*G21</f>
+        <f t="shared" si="2"/>
         <v>54495.041379310343</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="3">
-        <f>K21/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <f>ROUNDDOWN(L21*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N21" s="10">
         <v>6481705</v>
       </c>
       <c r="O21" s="7" t="e">
-        <f>N21/K21</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="7" t="e">
-        <f>M21*O21</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17669,38 +17669,38 @@
         <v>4.6790165557010498E-6</v>
       </c>
       <c r="G22" s="1">
-        <f>ROUNDDOWN(F22*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H22" s="10">
         <v>1645813</v>
       </c>
       <c r="I22" s="7">
-        <f>H22/E22</f>
+        <f t="shared" si="1"/>
         <v>8896.286486486486</v>
       </c>
       <c r="J22" s="7">
-        <f>I22*G22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K22" s="1">
         <v>73</v>
       </c>
       <c r="L22" s="3">
-        <f>K22/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.8463146408982517E-6</v>
       </c>
       <c r="M22" s="1">
-        <f>ROUNDDOWN(L22*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N22" s="10"/>
       <c r="O22" s="7">
-        <f>N22/K22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P22" s="7">
-        <f>M22*O22</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -17719,34 +17719,34 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <f>ROUNDDOWN(F23*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="7" t="e">
-        <f>H23/E23</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f>I23*G23</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="3">
-        <f>K23/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f>ROUNDDOWN(L23*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="7" t="e">
-        <f>N23/K23</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="7" t="e">
-        <f>M23*O23</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17765,34 +17765,34 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <f>ROUNDDOWN(F24*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="7" t="e">
-        <f>H24/E24</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f>I24*G24</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="3">
-        <f>K24/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>ROUNDDOWN(L24*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="7" t="e">
-        <f>N24/K24</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="7" t="e">
-        <f>M24*O24</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17813,40 +17813,40 @@
         <v>1.43961958027299E-4</v>
       </c>
       <c r="G25" s="1">
-        <f>ROUNDDOWN(F25*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
       </c>
       <c r="I25" s="7">
-        <f>H25/E25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="7">
-        <f>I25*G25</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K25" s="1">
         <v>3293</v>
       </c>
       <c r="L25" s="3">
-        <f>K25/$E$5</f>
+        <f t="shared" si="3"/>
         <v>8.3286494691478673E-5</v>
       </c>
       <c r="M25" s="1">
-        <f>ROUNDDOWN(L25*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="N25" s="10">
         <v>0</v>
       </c>
       <c r="O25" s="7">
-        <f>N25/K25</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P25" s="7">
-        <f>M25*O25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -17867,40 +17867,40 @@
         <v>3.3261484715688897E-4</v>
       </c>
       <c r="G26" s="1">
-        <f>ROUNDDOWN(F26*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H26" s="10">
         <v>26912115</v>
       </c>
       <c r="I26" s="7">
-        <f>H26/E26</f>
+        <f t="shared" si="1"/>
         <v>2046.3930499581782</v>
       </c>
       <c r="J26" s="7">
-        <f>I26*G26</f>
+        <f t="shared" si="2"/>
         <v>122783.5829974907</v>
       </c>
       <c r="K26" s="1">
         <v>6358</v>
       </c>
       <c r="L26" s="3">
-        <f>K26/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.6080641762782308E-4</v>
       </c>
       <c r="M26" s="1">
-        <f>ROUNDDOWN(L26*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="N26" s="10">
         <v>19874738</v>
       </c>
       <c r="O26" s="7">
-        <f>N26/K26</f>
+        <f t="shared" si="5"/>
         <v>3125.9418055992451</v>
       </c>
       <c r="P26" s="7">
-        <f>M26*O26</f>
+        <f t="shared" si="6"/>
         <v>90652.312362378114</v>
       </c>
     </row>
@@ -17921,40 +17921,40 @@
         <v>2.9009902645346498E-5</v>
       </c>
       <c r="G27" s="1">
-        <f>ROUNDDOWN(F27*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="H27" s="10">
         <v>12314110</v>
       </c>
       <c r="I27" s="7">
-        <f>H27/E27</f>
+        <f t="shared" si="1"/>
         <v>10735.928509154315</v>
       </c>
       <c r="J27" s="7">
-        <f>I27*G27</f>
+        <f t="shared" si="2"/>
         <v>53679.642545771574</v>
       </c>
       <c r="K27" s="1">
         <v>1607</v>
       </c>
       <c r="L27" s="3">
-        <f>K27/$E$5</f>
+        <f t="shared" si="3"/>
         <v>4.0644214081143708E-5</v>
       </c>
       <c r="M27" s="1">
-        <f>ROUNDDOWN(L27*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="N27" s="10">
         <v>6679784</v>
       </c>
       <c r="O27" s="7">
-        <f>N27/K27</f>
+        <f t="shared" si="5"/>
         <v>4156.6795270690727</v>
       </c>
       <c r="P27" s="7">
-        <f>M27*O27</f>
+        <f t="shared" si="6"/>
         <v>29096.756689483511</v>
       </c>
     </row>
@@ -17975,40 +17975,40 @@
         <v>3.87473154774811E-5</v>
       </c>
       <c r="G28" s="1">
-        <f>ROUNDDOWN(F28*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="H28" s="10">
         <v>8602104</v>
       </c>
       <c r="I28" s="7">
-        <f>H28/E28</f>
+        <f t="shared" si="1"/>
         <v>5614.9503916449084</v>
       </c>
       <c r="J28" s="7">
-        <f>I28*G28</f>
+        <f t="shared" si="2"/>
         <v>39304.652741514357</v>
       </c>
       <c r="K28" s="1">
         <v>654</v>
       </c>
       <c r="L28" s="3">
-        <f>K28/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.6540955823937764E-5</v>
       </c>
       <c r="M28" s="1">
-        <f>ROUNDDOWN(L28*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N28" s="10">
         <v>3296636</v>
       </c>
       <c r="O28" s="7">
-        <f>N28/K28</f>
+        <f t="shared" si="5"/>
         <v>5040.7278287461777</v>
       </c>
       <c r="P28" s="7">
-        <f>M28*O28</f>
+        <f t="shared" si="6"/>
         <v>15122.183486238533</v>
       </c>
     </row>
@@ -18029,40 +18029,40 @@
         <v>1.61160505367173E-4</v>
       </c>
       <c r="G29" s="1">
-        <f>ROUNDDOWN(F29*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="H29" s="10">
         <v>23133897</v>
       </c>
       <c r="I29" s="7">
-        <f>H29/E29</f>
+        <f t="shared" si="1"/>
         <v>3630.5550847457625</v>
       </c>
       <c r="J29" s="7">
-        <f>I29*G29</f>
+        <f t="shared" si="2"/>
         <v>105286.09745762711</v>
       </c>
       <c r="K29" s="1">
         <v>2480</v>
       </c>
       <c r="L29" s="3">
-        <f>K29/$E$5</f>
+        <f t="shared" si="3"/>
         <v>6.2724113827776229E-5</v>
       </c>
       <c r="M29" s="1">
-        <f>ROUNDDOWN(L29*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="N29" s="10">
         <v>8417839</v>
       </c>
       <c r="O29" s="7">
-        <f>N29/K29</f>
+        <f t="shared" si="5"/>
         <v>3394.2899193548387</v>
       </c>
       <c r="P29" s="7">
-        <f>M29*O29</f>
+        <f t="shared" si="6"/>
         <v>37337.189112903223</v>
       </c>
     </row>
@@ -18083,40 +18083,40 @@
         <v>8.3514122523918203E-5</v>
       </c>
       <c r="G30" s="1">
-        <f>ROUNDDOWN(F30*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="H30" s="10">
         <v>8864419</v>
       </c>
       <c r="I30" s="7">
-        <f>H30/E30</f>
+        <f t="shared" si="1"/>
         <v>2684.5605693519078</v>
       </c>
       <c r="J30" s="7">
-        <f>I30*G30</f>
+        <f t="shared" si="2"/>
         <v>40268.408540278615</v>
       </c>
       <c r="K30" s="1">
         <v>774</v>
       </c>
       <c r="L30" s="3">
-        <f>K30/$E$5</f>
+        <f t="shared" si="3"/>
         <v>1.9575993589797902E-5</v>
       </c>
       <c r="M30" s="1">
-        <f>ROUNDDOWN(L30*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N30" s="10">
         <v>2366193</v>
       </c>
       <c r="O30" s="7">
-        <f>N30/K30</f>
+        <f t="shared" si="5"/>
         <v>3057.0968992248063</v>
       </c>
       <c r="P30" s="7">
-        <f>M30*O30</f>
+        <f t="shared" si="6"/>
         <v>9171.2906976744198</v>
       </c>
     </row>
@@ -18137,40 +18137,40 @@
         <v>8.1693099864402093E-6</v>
       </c>
       <c r="G31" s="1">
-        <f>ROUNDDOWN(F31*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H31" s="10">
         <v>1123833</v>
       </c>
       <c r="I31" s="7">
-        <f>H31/E31</f>
+        <f t="shared" si="1"/>
         <v>3479.3591331269349</v>
       </c>
       <c r="J31" s="7">
-        <f>I31*G31</f>
+        <f t="shared" si="2"/>
         <v>3479.3591331269349</v>
       </c>
       <c r="K31" s="1">
         <v>23</v>
       </c>
       <c r="L31" s="3">
-        <f>K31/$E$5</f>
+        <f t="shared" si="3"/>
         <v>5.8171557178986015E-7</v>
       </c>
       <c r="M31" s="1">
-        <f>ROUNDDOWN(L31*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N31" s="10">
         <v>3364</v>
       </c>
       <c r="O31" s="7">
-        <f>N31/K31</f>
+        <f t="shared" si="5"/>
         <v>146.2608695652174</v>
       </c>
       <c r="P31" s="7">
-        <f>M31*O31</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -18191,40 +18191,40 @@
         <v>6.3052909585744403E-5</v>
       </c>
       <c r="G32" s="1">
-        <f>ROUNDDOWN(F32*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="H32" s="10">
         <v>34381477</v>
       </c>
       <c r="I32" s="7">
-        <f>H32/E32</f>
+        <f t="shared" si="1"/>
         <v>13791.20617729643</v>
       </c>
       <c r="J32" s="7">
-        <f>I32*G32</f>
+        <f t="shared" si="2"/>
         <v>151703.26795026072</v>
       </c>
       <c r="K32" s="1">
         <v>1017</v>
       </c>
       <c r="L32" s="3">
-        <f>K32/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.5721945065664686E-5</v>
       </c>
       <c r="M32" s="1">
-        <f>ROUNDDOWN(L32*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N32" s="10">
         <v>15458352</v>
       </c>
       <c r="O32" s="7">
-        <f>N32/K32</f>
+        <f t="shared" si="5"/>
         <v>15199.952802359881</v>
       </c>
       <c r="P32" s="7">
-        <f>M32*O32</f>
+        <f t="shared" si="6"/>
         <v>60799.811209439526</v>
       </c>
     </row>
@@ -18243,34 +18243,34 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <f>ROUNDDOWN(F33*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="7" t="e">
-        <f>H33/E33</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="7" t="e">
-        <f>I33*G33</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="3">
-        <f>K33/$E$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f>ROUNDDOWN(L33*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="7" t="e">
-        <f>N33/K33</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="7" t="e">
-        <f>M33*O33</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -18291,40 +18291,40 @@
         <v>8.1035508348465698E-5</v>
       </c>
       <c r="G34" s="1">
-        <f>ROUNDDOWN(F34*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="H34" s="10">
         <v>33552417</v>
       </c>
       <c r="I34" s="7">
-        <f>H34/E34</f>
+        <f t="shared" si="1"/>
         <v>10472.040262172284</v>
       </c>
       <c r="J34" s="7">
-        <f>I34*G34</f>
+        <f t="shared" si="2"/>
         <v>146608.56367041197</v>
       </c>
       <c r="K34" s="1">
         <v>972</v>
       </c>
       <c r="L34" s="3">
-        <f>K34/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.4583805903467134E-5</v>
       </c>
       <c r="M34" s="1">
-        <f>ROUNDDOWN(L34*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N34" s="10">
         <v>13355303</v>
       </c>
       <c r="O34" s="7">
-        <f>N34/K34</f>
+        <f t="shared" si="5"/>
         <v>13740.023662551441</v>
       </c>
       <c r="P34" s="7">
-        <f>M34*O34</f>
+        <f t="shared" si="6"/>
         <v>54960.094650205763</v>
       </c>
     </row>
@@ -18345,40 +18345,40 @@
         <v>5.4731847711011198E-5</v>
       </c>
       <c r="G35" s="1">
-        <f>ROUNDDOWN(F35*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H35" s="10">
         <v>25355911</v>
       </c>
       <c r="I35" s="7">
-        <f>H35/E35</f>
+        <f t="shared" si="1"/>
         <v>11717.149260628466</v>
       </c>
       <c r="J35" s="7">
-        <f>I35*G35</f>
+        <f t="shared" si="2"/>
         <v>105454.34334565621</v>
       </c>
       <c r="K35" s="1">
         <v>967</v>
       </c>
       <c r="L35" s="3">
-        <f>K35/$E$5</f>
+        <f t="shared" si="3"/>
         <v>2.4457345996556296E-5</v>
       </c>
       <c r="M35" s="1">
-        <f>ROUNDDOWN(L35*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N35" s="10">
         <v>13821124</v>
       </c>
       <c r="O35" s="7">
-        <f>N35/K35</f>
+        <f t="shared" si="5"/>
         <v>14292.785935884178</v>
       </c>
       <c r="P35" s="7">
-        <f>M35*O35</f>
+        <f t="shared" si="6"/>
         <v>57171.143743536712</v>
       </c>
     </row>
@@ -18399,46 +18399,46 @@
         <v>7.3928461580076598E-5</v>
       </c>
       <c r="G36" s="1">
-        <f>ROUNDDOWN(F36*$E$6,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="H36" s="10">
         <v>1182816</v>
       </c>
       <c r="I36" s="7">
-        <f>H36/E36</f>
+        <f t="shared" si="1"/>
         <v>404.65822784810126</v>
       </c>
       <c r="J36" s="7">
-        <f>I36*G36</f>
+        <f t="shared" si="2"/>
         <v>5260.5569620253164</v>
       </c>
       <c r="K36" s="1">
         <v>1291</v>
       </c>
       <c r="L36" s="3">
-        <f>K36/$E$5</f>
+        <f t="shared" si="3"/>
         <v>3.2651947964378669E-5</v>
       </c>
       <c r="M36" s="1">
-        <f>ROUNDDOWN(L36*$E$6,0)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="N36" s="11">
         <v>849931</v>
       </c>
       <c r="O36" s="7">
-        <f>N36/K36</f>
+        <f t="shared" si="5"/>
         <v>658.35089078233932</v>
       </c>
       <c r="P36" s="7">
-        <f>M36*O36</f>
+        <f t="shared" si="6"/>
         <v>3291.7544539116966</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="J37" s="7">
-        <f t="shared" ref="J8:J38" si="0">I37*G37</f>
+        <f t="shared" ref="J37:J38" si="7">I37*G37</f>
         <v>0</v>
       </c>
       <c r="L37" s="3"/>
@@ -18456,11 +18456,11 @@
         <v>309</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" ref="I9:I38" si="1">H38/E38</f>
+        <f t="shared" ref="I38" si="8">H38/E38</f>
         <v>0</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L38" s="3"/>
@@ -18633,44 +18633,44 @@
         <v>1434</v>
       </c>
       <c r="F7" s="3">
-        <f>E7/$E$5</f>
+        <f t="shared" ref="F7:F36" si="0">E7/$E$5</f>
         <v>3.6625614222916211E-5</v>
       </c>
       <c r="G7" s="1">
-        <f>ROUNDDOWN(F7*$E$6,0)</f>
+        <f t="shared" ref="G7:G36" si="1">ROUNDDOWN(F7*$E$6,0)</f>
         <v>6</v>
       </c>
       <c r="H7" s="10">
         <v>16072685</v>
       </c>
       <c r="I7" s="7">
-        <f>H7/E7</f>
+        <f t="shared" ref="I7:I36" si="2">H7/E7</f>
         <v>11208.288005578801</v>
       </c>
       <c r="J7" s="7">
-        <f>I7*G7</f>
+        <f t="shared" ref="J7:J36" si="3">I7*G7</f>
         <v>67249.728033472813</v>
       </c>
       <c r="K7" s="1">
         <v>586</v>
       </c>
       <c r="L7" s="3">
-        <f>K7/$E$5</f>
+        <f t="shared" ref="L7:L36" si="4">K7/$E$5</f>
         <v>1.4966952534608715E-5</v>
       </c>
       <c r="M7" s="1">
-        <f>ROUNDDOWN(L7*$E$6,0)</f>
+        <f t="shared" ref="M7:M36" si="5">ROUNDDOWN(L7*$E$6,0)</f>
         <v>2</v>
       </c>
       <c r="N7" s="10">
         <v>7486935</v>
       </c>
       <c r="O7" s="7">
-        <f>N7/K7</f>
+        <f t="shared" ref="O7:O36" si="6">N7/K7</f>
         <v>12776.339590443686</v>
       </c>
       <c r="P7" s="7">
-        <f>M7*O7</f>
+        <f t="shared" ref="P7:P36" si="7">M7*O7</f>
         <v>25552.679180887371</v>
       </c>
     </row>
@@ -18688,44 +18688,44 @@
         <v>3017</v>
       </c>
       <c r="F8" s="3">
-        <f>E8/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.7056818766065691E-5</v>
       </c>
       <c r="G8" s="1">
-        <f>ROUNDDOWN(F8*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="H8" s="10">
         <v>403661227</v>
       </c>
       <c r="I8" s="7">
-        <f>H8/E8</f>
+        <f t="shared" si="2"/>
         <v>133795.56745111037</v>
       </c>
       <c r="J8" s="7">
-        <f>I8*G8</f>
+        <f t="shared" si="3"/>
         <v>1739342.3768644349</v>
       </c>
       <c r="K8" s="1">
         <v>519</v>
       </c>
       <c r="L8" s="3">
-        <f>K8/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.3255713934235363E-5</v>
       </c>
       <c r="M8" s="1">
-        <f>ROUNDDOWN(L8*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N8" s="10">
         <v>56658307</v>
       </c>
       <c r="O8" s="7">
-        <f>N8/K8</f>
+        <f t="shared" si="6"/>
         <v>109168.22157996146</v>
       </c>
       <c r="P8" s="7">
-        <f>M8*O8</f>
+        <f t="shared" si="7"/>
         <v>218336.44315992293</v>
       </c>
     </row>
@@ -18741,38 +18741,38 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="3">
-        <f>E9/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <f>ROUNDDOWN(F9*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="7" t="e">
-        <f>H9/E9</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="7" t="e">
-        <f>I9*G9</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="3">
-        <f>K9/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f>ROUNDDOWN(L9*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="7" t="e">
-        <f>N9/K9</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="7" t="e">
-        <f>M9*O9</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -18790,44 +18790,44 @@
         <v>3023</v>
       </c>
       <c r="F10" s="3">
-        <f>E10/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.7210064013860321E-5</v>
       </c>
       <c r="G10" s="1">
-        <f>ROUNDDOWN(F10*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="H10" s="10">
         <v>183928230</v>
       </c>
       <c r="I10" s="7">
-        <f>H10/E10</f>
+        <f t="shared" si="2"/>
         <v>60842.947403241815</v>
       </c>
       <c r="J10" s="7">
-        <f>I10*G10</f>
+        <f t="shared" si="3"/>
         <v>790958.31624214363</v>
       </c>
       <c r="K10" s="1">
         <v>1378</v>
       </c>
       <c r="L10" s="3">
-        <f>K10/$E$5</f>
+        <f t="shared" si="4"/>
         <v>3.5195325243499672E-5</v>
       </c>
       <c r="M10" s="1">
-        <f>ROUNDDOWN(L10*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="N10" s="10">
         <v>93927669</v>
       </c>
       <c r="O10" s="7">
-        <f>N10/K10</f>
+        <f t="shared" si="6"/>
         <v>68162.314223512338</v>
       </c>
       <c r="P10" s="7">
-        <f>M10*O10</f>
+        <f t="shared" si="7"/>
         <v>408973.88534107403</v>
       </c>
     </row>
@@ -18845,42 +18845,42 @@
         <v>2455</v>
       </c>
       <c r="F11" s="3">
-        <f>E11/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.2702847222635482E-5</v>
       </c>
       <c r="G11" s="1">
-        <f>ROUNDDOWN(F11*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="H11" s="10">
         <v>38545383</v>
       </c>
       <c r="I11" s="7">
-        <f>H11/E11</f>
+        <f t="shared" si="2"/>
         <v>15700.76700610998</v>
       </c>
       <c r="J11" s="7">
-        <f>I11*G11</f>
+        <f t="shared" si="3"/>
         <v>172708.43706720977</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="3">
-        <f>K11/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <f>ROUNDDOWN(L11*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N11" s="10">
         <v>19822357</v>
       </c>
       <c r="O11" s="7" t="e">
-        <f>N11/K11</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="7" t="e">
-        <f>M11*O11</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -18898,44 +18898,44 @@
         <v>262</v>
       </c>
       <c r="F12" s="3">
-        <f>E12/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.6917091536987771E-6</v>
       </c>
       <c r="G12" s="1">
-        <f>ROUNDDOWN(F12*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H12" s="10">
         <v>6639</v>
       </c>
       <c r="I12" s="7">
-        <f>H12/E12</f>
+        <f t="shared" si="2"/>
         <v>25.33969465648855</v>
       </c>
       <c r="J12" s="7">
-        <f>I12*G12</f>
+        <f t="shared" si="3"/>
         <v>25.33969465648855</v>
       </c>
       <c r="K12" s="1">
         <v>55</v>
       </c>
       <c r="L12" s="3">
-        <f>K12/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.4047481047840945E-6</v>
       </c>
       <c r="M12" s="1">
-        <f>ROUNDDOWN(L12*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N12" s="10">
         <v>120</v>
       </c>
       <c r="O12" s="7">
-        <f>N12/K12</f>
+        <f t="shared" si="6"/>
         <v>2.1818181818181817</v>
       </c>
       <c r="P12" s="7">
-        <f>M12*O12</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -18953,44 +18953,44 @@
         <v>188</v>
       </c>
       <c r="F13" s="3">
-        <f>E13/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.8016844308983595E-6</v>
       </c>
       <c r="G13" s="1">
-        <f>ROUNDDOWN(F13*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H13" s="10">
         <v>27521424</v>
       </c>
       <c r="I13" s="7">
-        <f>H13/E13</f>
+        <f t="shared" si="2"/>
         <v>146390.55319148937</v>
       </c>
       <c r="J13" s="7">
-        <f>I13*G13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K13" s="1">
         <v>58</v>
       </c>
       <c r="L13" s="3">
-        <f>K13/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.4813707286814086E-6</v>
       </c>
       <c r="M13" s="1">
-        <f>ROUNDDOWN(L13*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N13" s="10">
         <v>1802512</v>
       </c>
       <c r="O13" s="7">
-        <f>N13/K13</f>
+        <f t="shared" si="6"/>
         <v>31077.793103448275</v>
       </c>
       <c r="P13" s="7">
-        <f>M13*O13</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19008,44 +19008,44 @@
         <v>1944</v>
       </c>
       <c r="F14" s="3">
-        <f>E14/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.9651460285459632E-5</v>
       </c>
       <c r="G14" s="1">
-        <f>ROUNDDOWN(F14*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="H14" s="10">
         <v>7769432</v>
       </c>
       <c r="I14" s="7">
-        <f>H14/E14</f>
+        <f t="shared" si="2"/>
         <v>3996.6213991769546</v>
       </c>
       <c r="J14" s="7">
-        <f>I14*G14</f>
+        <f t="shared" si="3"/>
         <v>31972.971193415637</v>
       </c>
       <c r="K14" s="1">
         <v>921</v>
       </c>
       <c r="L14" s="3">
-        <f>K14/$E$5</f>
+        <f t="shared" si="4"/>
         <v>2.3523145536475471E-5</v>
       </c>
       <c r="M14" s="1">
-        <f>ROUNDDOWN(L14*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="N14" s="10">
         <v>3832132</v>
       </c>
       <c r="O14" s="7">
-        <f>N14/K14</f>
+        <f t="shared" si="6"/>
         <v>4160.8382193268189</v>
       </c>
       <c r="P14" s="7">
-        <f>M14*O14</f>
+        <f t="shared" si="7"/>
         <v>16643.352877307276</v>
       </c>
     </row>
@@ -19063,44 +19063,44 @@
         <v>5838</v>
       </c>
       <c r="F15" s="3">
-        <f>E15/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.4910762610417352E-4</v>
       </c>
       <c r="G15" s="1">
-        <f>ROUNDDOWN(F15*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="H15" s="10">
         <v>11613542</v>
       </c>
       <c r="I15" s="7">
-        <f>H15/E15</f>
+        <f t="shared" si="2"/>
         <v>1989.3014731072285</v>
       </c>
       <c r="J15" s="7">
-        <f>I15*G15</f>
+        <f t="shared" si="3"/>
         <v>53711.139773895171</v>
       </c>
       <c r="K15" s="1">
         <v>870</v>
       </c>
       <c r="L15" s="3">
-        <f>K15/$E$5</f>
+        <f t="shared" si="4"/>
         <v>2.222056093022113E-5</v>
       </c>
       <c r="M15" s="1">
-        <f>ROUNDDOWN(L15*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="N15" s="10">
         <v>4535685</v>
       </c>
       <c r="O15" s="7">
-        <f>N15/K15</f>
+        <f t="shared" si="6"/>
         <v>5213.4310344827591</v>
       </c>
       <c r="P15" s="7">
-        <f>M15*O15</f>
+        <f t="shared" si="7"/>
         <v>20853.724137931036</v>
       </c>
     </row>
@@ -19118,42 +19118,42 @@
         <v>1347</v>
       </c>
       <c r="F16" s="3">
-        <f>E16/$E$5</f>
+        <f t="shared" si="0"/>
         <v>3.4403558129894097E-5</v>
       </c>
       <c r="G16" s="1">
-        <f>ROUNDDOWN(F16*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="H16" s="10">
         <v>29149623</v>
       </c>
       <c r="I16" s="7">
-        <f>H16/E16</f>
+        <f t="shared" si="2"/>
         <v>21640.403118040089</v>
       </c>
       <c r="J16" s="7">
-        <f>I16*G16</f>
+        <f t="shared" si="3"/>
         <v>129842.41870824053</v>
       </c>
       <c r="K16" s="1">
         <v>248</v>
       </c>
       <c r="L16" s="3">
-        <f>K16/$E$5</f>
+        <f t="shared" si="4"/>
         <v>6.334136908844644E-6</v>
       </c>
       <c r="M16" s="1">
-        <f>ROUNDDOWN(L16*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="7">
-        <f>N16/K16</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P16" s="7">
-        <f>M16*O16</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19169,38 +19169,38 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="3">
-        <f>E17/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <f>ROUNDDOWN(F17*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="7" t="e">
-        <f>H17/E17</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="7" t="e">
-        <f>I17*G17</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="3">
-        <f>K17/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f>ROUNDDOWN(L17*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="7" t="e">
-        <f>N17/K17</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="7" t="e">
-        <f>M17*O17</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19218,44 +19218,44 @@
         <v>618</v>
       </c>
       <c r="F18" s="3">
-        <f>E18/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.5784260522846734E-5</v>
       </c>
       <c r="G18" s="1">
-        <f>ROUNDDOWN(F18*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H18" s="10">
         <v>1675402</v>
       </c>
       <c r="I18" s="7">
-        <f>H18/E18</f>
+        <f t="shared" si="2"/>
         <v>2711.0064724919093</v>
       </c>
       <c r="J18" s="7">
-        <f>I18*G18</f>
+        <f t="shared" si="3"/>
         <v>5422.0129449838187</v>
       </c>
       <c r="K18" s="1">
         <v>254</v>
       </c>
       <c r="L18" s="3">
-        <f>K18/$E$5</f>
+        <f t="shared" si="4"/>
         <v>6.4873821566392727E-6</v>
       </c>
       <c r="M18" s="1">
-        <f>ROUNDDOWN(L18*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N18" s="10">
         <v>1124517</v>
       </c>
       <c r="O18" s="7">
-        <f>N18/K18</f>
+        <f t="shared" si="6"/>
         <v>4427.2322834645665</v>
       </c>
       <c r="P18" s="7">
-        <f>M18*O18</f>
+        <f t="shared" si="7"/>
         <v>4427.2322834645665</v>
       </c>
     </row>
@@ -19273,44 +19273,44 @@
         <v>3759</v>
       </c>
       <c r="F19" s="3">
-        <f>E19/$E$5</f>
+        <f t="shared" si="0"/>
         <v>9.6008147743334744E-5</v>
       </c>
       <c r="G19" s="1">
-        <f>ROUNDDOWN(F19*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="H19" s="10">
         <v>53179827</v>
       </c>
       <c r="I19" s="7">
-        <f>H19/E19</f>
+        <f t="shared" si="2"/>
         <v>14147.333599361533</v>
       </c>
       <c r="J19" s="7">
-        <f>I19*G19</f>
+        <f t="shared" si="3"/>
         <v>240504.67118914606</v>
       </c>
       <c r="K19" s="1">
         <v>1292</v>
       </c>
       <c r="L19" s="3">
-        <f>K19/$E$5</f>
+        <f t="shared" si="4"/>
         <v>3.2998810025110001E-5</v>
       </c>
       <c r="M19" s="1">
-        <f>ROUNDDOWN(L19*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="N19" s="10">
         <v>23891606</v>
       </c>
       <c r="O19" s="7">
-        <f>N19/K19</f>
+        <f t="shared" si="6"/>
         <v>18491.955108359132</v>
       </c>
       <c r="P19" s="7">
-        <f>M19*O19</f>
+        <f t="shared" si="7"/>
         <v>92459.775541795665</v>
       </c>
     </row>
@@ -19328,44 +19328,44 @@
         <v>3153</v>
       </c>
       <c r="F20" s="3">
-        <f>E20/$E$5</f>
+        <f t="shared" si="0"/>
         <v>8.0530377716077264E-5</v>
       </c>
       <c r="G20" s="1">
-        <f>ROUNDDOWN(F20*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="H20" s="10">
         <v>292951498</v>
       </c>
       <c r="I20" s="7">
-        <f>H20/E20</f>
+        <f t="shared" si="2"/>
         <v>92911.987947986039</v>
       </c>
       <c r="J20" s="7">
-        <f>I20*G20</f>
+        <f t="shared" si="3"/>
         <v>1300767.8312718046</v>
       </c>
       <c r="K20" s="1">
         <v>1312</v>
       </c>
       <c r="L20" s="3">
-        <f>K20/$E$5</f>
+        <f t="shared" si="4"/>
         <v>3.3509627517758764E-5</v>
       </c>
       <c r="M20" s="1">
-        <f>ROUNDDOWN(L20*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="N20" s="10">
         <v>115015665</v>
       </c>
       <c r="O20" s="7">
-        <f>N20/K20</f>
+        <f t="shared" si="6"/>
         <v>87664.378810975613</v>
       </c>
       <c r="P20" s="7">
-        <f>M20*O20</f>
+        <f t="shared" si="7"/>
         <v>525986.27286585374</v>
       </c>
     </row>
@@ -19383,44 +19383,44 @@
         <v>547</v>
       </c>
       <c r="F21" s="3">
-        <f>E21/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.3970858423943629E-5</v>
       </c>
       <c r="G21" s="1">
-        <f>ROUNDDOWN(F21*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H21" s="10">
         <v>12612922</v>
       </c>
       <c r="I21" s="7">
-        <f>H21/E21</f>
+        <f t="shared" si="2"/>
         <v>23058.358318098719</v>
       </c>
       <c r="J21" s="7">
-        <f>I21*G21</f>
+        <f t="shared" si="3"/>
         <v>46116.716636197438</v>
       </c>
       <c r="K21" s="1">
         <v>184</v>
       </c>
       <c r="L21" s="3">
-        <f>K21/$E$5</f>
+        <f t="shared" si="4"/>
         <v>4.6995209323686065E-6</v>
       </c>
       <c r="M21" s="1">
-        <f>ROUNDDOWN(L21*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N21" s="10">
         <v>6781074</v>
       </c>
       <c r="O21" s="7">
-        <f>N21/K21</f>
+        <f t="shared" si="6"/>
         <v>36853.663043478264</v>
       </c>
       <c r="P21" s="7">
-        <f>M21*O21</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19438,44 +19438,44 @@
         <v>118</v>
       </c>
       <c r="F22" s="3">
-        <f>E22/$E$5</f>
+        <f t="shared" si="0"/>
         <v>3.0138232066276933E-6</v>
       </c>
       <c r="G22" s="1">
-        <f>ROUNDDOWN(F22*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H22" s="10">
         <v>528695</v>
       </c>
       <c r="I22" s="7">
-        <f>H22/E22</f>
+        <f t="shared" si="2"/>
         <v>4480.4661016949149</v>
       </c>
       <c r="J22" s="7">
-        <f>I22*G22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K22" s="1">
         <v>52</v>
       </c>
       <c r="L22" s="3">
-        <f>K22/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.3281254808867801E-6</v>
       </c>
       <c r="M22" s="1">
-        <f>ROUNDDOWN(L22*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N22" s="10">
         <v>136679</v>
       </c>
       <c r="O22" s="7">
-        <f>N22/K22</f>
+        <f t="shared" si="6"/>
         <v>2628.4423076923076</v>
       </c>
       <c r="P22" s="7">
-        <f>M22*O22</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19491,38 +19491,38 @@
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="3">
-        <f>E23/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <f>ROUNDDOWN(F23*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="7" t="e">
-        <f>H23/E23</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f>I23*G23</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="3">
-        <f>K23/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f>ROUNDDOWN(L23*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="7" t="e">
-        <f>N23/K23</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="7" t="e">
-        <f>M23*O23</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19538,38 +19538,38 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="3">
-        <f>E24/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <f>ROUNDDOWN(F24*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="7" t="e">
-        <f>H24/E24</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f>I24*G24</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="3">
-        <f>K24/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>ROUNDDOWN(L24*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="7" t="e">
-        <f>N24/K24</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="7" t="e">
-        <f>M24*O24</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19587,44 +19587,44 @@
         <v>11004</v>
       </c>
       <c r="F25" s="3">
-        <f>E25/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.8105178445534865E-4</v>
       </c>
       <c r="G25" s="1">
-        <f>ROUNDDOWN(F25*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="H25" s="10">
         <v>601</v>
       </c>
       <c r="I25" s="7">
-        <f>H25/E25</f>
+        <f t="shared" si="2"/>
         <v>5.461650308978553E-2</v>
       </c>
       <c r="J25" s="7">
-        <f>I25*G25</f>
+        <f t="shared" si="3"/>
         <v>2.7308251544892763</v>
       </c>
       <c r="K25" s="1">
         <v>6394</v>
       </c>
       <c r="L25" s="3">
-        <f>K25/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.633083523998091E-4</v>
       </c>
       <c r="M25" s="1">
-        <f>ROUNDDOWN(L25*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="N25" s="10">
         <v>0</v>
       </c>
       <c r="O25" s="7">
-        <f>N25/K25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P25" s="7">
-        <f>M25*O25</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19642,44 +19642,44 @@
         <v>9942</v>
       </c>
       <c r="F26" s="3">
-        <f>E26/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.5392737559569938E-4</v>
       </c>
       <c r="G26" s="1">
-        <f>ROUNDDOWN(F26*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="H26" s="10">
         <v>51478257</v>
       </c>
       <c r="I26" s="7">
-        <f>H26/E26</f>
+        <f t="shared" si="2"/>
         <v>5177.8572721786359</v>
       </c>
       <c r="J26" s="7">
-        <f>I26*G26</f>
+        <f t="shared" si="3"/>
         <v>238181.43452021724</v>
       </c>
       <c r="K26" s="1">
         <v>5462</v>
       </c>
       <c r="L26" s="3">
-        <f>K26/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.395042572423768E-4</v>
       </c>
       <c r="M26" s="1">
-        <f>ROUNDDOWN(L26*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="N26" s="10">
         <v>33406518</v>
       </c>
       <c r="O26" s="7">
-        <f>N26/K26</f>
+        <f t="shared" si="6"/>
         <v>6116.1695349688762</v>
       </c>
       <c r="P26" s="7">
-        <f>M26*O26</f>
+        <f t="shared" si="7"/>
         <v>152904.2383742219</v>
       </c>
     </row>
@@ -19697,44 +19697,44 @@
         <v>1538</v>
       </c>
       <c r="F27" s="3">
-        <f>E27/$E$5</f>
+        <f t="shared" si="0"/>
         <v>3.9281865184689766E-5</v>
       </c>
       <c r="G27" s="1">
-        <f>ROUNDDOWN(F27*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="H27" s="10">
         <v>6020695</v>
       </c>
       <c r="I27" s="7">
-        <f>H27/E27</f>
+        <f t="shared" si="2"/>
         <v>3914.6261378413524</v>
       </c>
       <c r="J27" s="7">
-        <f>I27*G27</f>
+        <f t="shared" si="3"/>
         <v>27402.382964889468</v>
       </c>
       <c r="K27" s="1">
         <v>1125</v>
       </c>
       <c r="L27" s="3">
-        <f>K27/$E$5</f>
+        <f t="shared" si="4"/>
         <v>2.873348396149284E-5</v>
       </c>
       <c r="M27" s="1">
-        <f>ROUNDDOWN(L27*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="N27" s="10">
         <v>4631542</v>
       </c>
       <c r="O27" s="7">
-        <f>N27/K27</f>
+        <f t="shared" si="6"/>
         <v>4116.9262222222223</v>
       </c>
       <c r="P27" s="7">
-        <f>M27*O27</f>
+        <f t="shared" si="7"/>
         <v>20584.631111111114</v>
       </c>
     </row>
@@ -19752,42 +19752,42 @@
         <v>862</v>
       </c>
       <c r="F28" s="3">
-        <f>E28/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.2016233933161627E-5</v>
       </c>
       <c r="G28" s="1">
-        <f>ROUNDDOWN(F28*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H28" s="10">
         <v>4889344</v>
       </c>
       <c r="I28" s="7">
-        <f>H28/E28</f>
+        <f t="shared" si="2"/>
         <v>5672.092807424594</v>
       </c>
       <c r="J28" s="7">
-        <f>I28*G28</f>
+        <f t="shared" si="3"/>
         <v>17016.278422273783</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="3">
-        <f>K28/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <f>ROUNDDOWN(L28*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N28" s="10">
         <v>2472096</v>
       </c>
       <c r="O28" s="7" t="e">
-        <f>N28/K28</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P28" s="7" t="e">
-        <f>M28*O28</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19805,44 +19805,44 @@
         <v>7244</v>
       </c>
       <c r="F29" s="3">
-        <f>E29/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.8501809583738144E-4</v>
       </c>
       <c r="G29" s="1">
-        <f>ROUNDDOWN(F29*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="H29" s="10">
         <v>86298197</v>
       </c>
       <c r="I29" s="7">
-        <f>H29/E29</f>
+        <f t="shared" si="2"/>
         <v>11913.058669243512</v>
       </c>
       <c r="J29" s="7">
-        <f>I29*G29</f>
+        <f t="shared" si="3"/>
         <v>393130.93608503591</v>
       </c>
       <c r="K29" s="1">
         <v>2853</v>
       </c>
       <c r="L29" s="3">
-        <f>K29/$E$5</f>
+        <f t="shared" si="4"/>
         <v>7.2868115326345839E-5</v>
       </c>
       <c r="M29" s="1">
-        <f>ROUNDDOWN(L29*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="N29" s="10">
         <v>21961851</v>
       </c>
       <c r="O29" s="7">
-        <f>N29/K29</f>
+        <f t="shared" si="6"/>
         <v>7697.8096740273395</v>
       </c>
       <c r="P29" s="7">
-        <f>M29*O29</f>
+        <f t="shared" si="7"/>
         <v>100071.52576235542</v>
       </c>
     </row>
@@ -19860,44 +19860,44 @@
         <v>2942</v>
       </c>
       <c r="F30" s="3">
-        <f>E30/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.5141253168632831E-5</v>
       </c>
       <c r="G30" s="1">
-        <f>ROUNDDOWN(F30*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="H30" s="10">
         <v>12884518</v>
       </c>
       <c r="I30" s="7">
-        <f>H30/E30</f>
+        <f t="shared" si="2"/>
         <v>4379.5098572399729</v>
       </c>
       <c r="J30" s="7">
-        <f>I30*G30</f>
+        <f t="shared" si="3"/>
         <v>56933.628144119648</v>
       </c>
       <c r="K30" s="1">
         <v>580</v>
       </c>
       <c r="L30" s="3">
-        <f>K30/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.4813707286814086E-5</v>
       </c>
       <c r="M30" s="1">
-        <f>ROUNDDOWN(L30*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N30" s="10">
         <v>4483537</v>
       </c>
       <c r="O30" s="7">
-        <f>N30/K30</f>
+        <f t="shared" si="6"/>
         <v>7730.2362068965522</v>
       </c>
       <c r="P30" s="7">
-        <f>M30*O30</f>
+        <f t="shared" si="7"/>
         <v>15460.472413793104</v>
       </c>
     </row>
@@ -19915,44 +19915,44 @@
         <v>441</v>
       </c>
       <c r="F31" s="3">
-        <f>E31/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.1263525712905194E-5</v>
       </c>
       <c r="G31" s="1">
-        <f>ROUNDDOWN(F31*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H31" s="10">
         <v>6398442</v>
       </c>
       <c r="I31" s="7">
-        <f>H31/E31</f>
+        <f t="shared" si="2"/>
         <v>14508.938775510203</v>
       </c>
       <c r="J31" s="7">
-        <f>I31*G31</f>
+        <f t="shared" si="3"/>
         <v>29017.877551020407</v>
       </c>
       <c r="K31" s="1">
         <v>39</v>
       </c>
       <c r="L31" s="3">
-        <f>K31/$E$5</f>
+        <f t="shared" si="4"/>
         <v>9.9609411066508508E-7</v>
       </c>
       <c r="M31" s="1">
-        <f>ROUNDDOWN(L31*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N31" s="10">
         <v>424623</v>
       </c>
       <c r="O31" s="7">
-        <f>N31/K31</f>
+        <f t="shared" si="6"/>
         <v>10887.76923076923</v>
       </c>
       <c r="P31" s="7">
-        <f>M31*O31</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19970,44 +19970,44 @@
         <v>2322</v>
       </c>
       <c r="F32" s="3">
-        <f>E32/$E$5</f>
+        <f t="shared" si="0"/>
         <v>5.9305910896521225E-5</v>
       </c>
       <c r="G32" s="1">
-        <f>ROUNDDOWN(F32*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="H32" s="10">
         <v>51648483</v>
       </c>
       <c r="I32" s="7">
-        <f>H32/E32</f>
+        <f t="shared" si="2"/>
         <v>22243.102067183463</v>
       </c>
       <c r="J32" s="7">
-        <f>I32*G32</f>
+        <f t="shared" si="3"/>
         <v>222431.02067183465</v>
       </c>
       <c r="K32" s="1">
         <v>936</v>
       </c>
       <c r="L32" s="3">
-        <f>K32/$E$5</f>
+        <f t="shared" si="4"/>
         <v>2.3906258655962044E-5</v>
       </c>
       <c r="M32" s="1">
-        <f>ROUNDDOWN(L32*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="N32" s="10">
         <v>33672648</v>
       </c>
       <c r="O32" s="7">
-        <f>N32/K32</f>
+        <f t="shared" si="6"/>
         <v>35975.051282051281</v>
       </c>
       <c r="P32" s="7">
-        <f>M32*O32</f>
+        <f t="shared" si="7"/>
         <v>143900.20512820513</v>
       </c>
     </row>
@@ -20023,38 +20023,38 @@
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="3">
-        <f>E33/$E$5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <f>ROUNDDOWN(F33*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="7" t="e">
-        <f>H33/E33</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="7" t="e">
-        <f>I33*G33</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="3">
-        <f>K33/$E$5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f>ROUNDDOWN(L33*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="7" t="e">
-        <f>N33/K33</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="7" t="e">
-        <f>M33*O33</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -20072,42 +20072,42 @@
         <v>2419</v>
       </c>
       <c r="F34" s="3">
-        <f>E34/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.1783375735867713E-5</v>
       </c>
       <c r="G34" s="1">
-        <f>ROUNDDOWN(F34*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="H34" s="10">
         <v>15397564</v>
       </c>
       <c r="I34" s="7">
-        <f>H34/E34</f>
+        <f t="shared" si="2"/>
         <v>6365.2600248036379</v>
       </c>
       <c r="J34" s="7">
-        <f>I34*G34</f>
+        <f t="shared" si="3"/>
         <v>70017.860272840015</v>
       </c>
       <c r="K34" s="1">
         <v>642</v>
       </c>
       <c r="L34" s="3">
-        <f>K34/$E$5</f>
+        <f t="shared" si="4"/>
         <v>1.6397241514025249E-5</v>
       </c>
       <c r="M34" s="1">
-        <f>ROUNDDOWN(L34*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N34" s="10"/>
       <c r="O34" s="7">
-        <f>N34/K34</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P34" s="7">
-        <f>M34*O34</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -20125,44 +20125,44 @@
         <v>3408</v>
       </c>
       <c r="F35" s="3">
-        <f>E35/$E$5</f>
+        <f t="shared" si="0"/>
         <v>8.7043300747348981E-5</v>
       </c>
       <c r="G35" s="1">
-        <f>ROUNDDOWN(F35*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="H35" s="10">
         <v>54843257</v>
       </c>
       <c r="I35" s="7">
-        <f>H35/E35</f>
+        <f t="shared" si="2"/>
         <v>16092.50498826291</v>
       </c>
       <c r="J35" s="7">
-        <f>I35*G35</f>
+        <f t="shared" si="3"/>
         <v>241387.57482394367</v>
       </c>
       <c r="K35" s="1">
         <v>1231</v>
       </c>
       <c r="L35" s="3">
-        <f>K35/$E$5</f>
+        <f t="shared" si="4"/>
         <v>3.1440816672531274E-5</v>
       </c>
       <c r="M35" s="1">
-        <f>ROUNDDOWN(L35*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="N35" s="10">
         <v>16112922</v>
       </c>
       <c r="O35" s="7">
-        <f>N35/K35</f>
+        <f t="shared" si="6"/>
         <v>13089.294882209586</v>
       </c>
       <c r="P35" s="7">
-        <f>M35*O35</f>
+        <f t="shared" si="7"/>
         <v>65446.47441104793</v>
       </c>
     </row>
@@ -20180,50 +20180,50 @@
         <v>1913</v>
       </c>
       <c r="F36" s="3">
-        <f>E36/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.885969317185405E-5</v>
       </c>
       <c r="G36" s="1">
-        <f>ROUNDDOWN(F36*$E$6,0)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="H36" s="10">
         <v>557421</v>
       </c>
       <c r="I36" s="7">
-        <f>H36/E36</f>
+        <f t="shared" si="2"/>
         <v>291.385781495034</v>
       </c>
       <c r="J36" s="7">
-        <f>I36*G36</f>
+        <f t="shared" si="3"/>
         <v>2331.086251960272</v>
       </c>
       <c r="K36" s="1">
         <v>965</v>
       </c>
       <c r="L36" s="3">
-        <f>K36/$E$5</f>
+        <f t="shared" si="4"/>
         <v>2.4646944020302749E-5</v>
       </c>
       <c r="M36" s="1">
-        <f>ROUNDDOWN(L36*$E$6,0)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="N36" s="10">
         <v>326868</v>
       </c>
       <c r="O36" s="7">
-        <f>N36/K36</f>
+        <f t="shared" si="6"/>
         <v>338.72331606217614</v>
       </c>
       <c r="P36" s="7">
-        <f>M36*O36</f>
+        <f t="shared" si="7"/>
         <v>1354.8932642487046</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="J37" s="7">
-        <f t="shared" ref="J8:J38" si="0">I37*G37</f>
+        <f t="shared" ref="J37:J38" si="8">I37*G37</f>
         <v>0</v>
       </c>
       <c r="L37" s="3"/>
@@ -20241,11 +20241,11 @@
         <v>312</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" ref="I9:I38" si="1">H38/E38</f>
+        <f t="shared" ref="I38" si="9">H38/E38</f>
         <v>0</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L38" s="3"/>
@@ -20306,23 +20306,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17" t="s">
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
@@ -20373,51 +20373,51 @@
         <v>2016</v>
       </c>
       <c r="C5" s="1">
-        <f>'2016_IC3 State to City'!$E$6</f>
+        <f>'2016_IC3 State to City CALIFORN'!$E$6</f>
         <v>177746</v>
       </c>
       <c r="F5">
-        <f>'2016_IC3 State to City'!$G$13</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$13</f>
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <f>'2016_IC3 State to City'!$G$29</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$29</f>
         <v>18</v>
       </c>
       <c r="H5">
-        <f>'2016_IC3 State to City'!$G$22</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$22</f>
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <f>'2016_IC3 State to City'!$G$30</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$30</f>
         <v>9</v>
       </c>
       <c r="J5" s="1">
-        <f>'2016_IC3 State to City'!$G$31</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$31</f>
         <v>1</v>
       </c>
       <c r="K5" s="1">
-        <f>'2016_IC3 State to City'!$G$12</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$12</f>
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <f>'2016_IC3 State to City'!$G$15</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$15</f>
         <v>10</v>
       </c>
       <c r="M5" s="1" t="e">
-        <f>'2016_IC3 State to City'!$G$36</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$36</f>
         <v>#REF!</v>
       </c>
       <c r="N5" s="1">
-        <f>'2016_IC3 State to City'!$G$18</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$18</f>
         <v>1</v>
       </c>
       <c r="O5" s="1">
-        <f>'2016_IC3 State to City'!$G$19</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$19</f>
         <v>10</v>
       </c>
       <c r="P5" s="1">
-        <f>'2016_IC3 State to City'!$G$8</f>
+        <f>'2016_IC3 State to City CALIFORN'!$G$8</f>
         <v>9</v>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
         <v>2017</v>
       </c>
       <c r="C6" s="1">
-        <f>'2017_IC3 State to City'!$E$6</f>
+        <f>'2017_IC3 State to City CALIFORN'!$E$6</f>
         <v>179530</v>
       </c>
       <c r="D6" s="1">
@@ -20434,47 +20434,47 @@
         <v>1784</v>
       </c>
       <c r="F6" s="1">
-        <f>'2017_IC3 State to City'!$G$13</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$13</f>
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <f>'2017_IC3 State to City'!$G$13</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$13</f>
         <v>2</v>
       </c>
       <c r="H6" s="1">
-        <f>'2017_IC3 State to City'!$G$22</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$22</f>
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <f>'2017_IC3 State to City'!$G$30</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$30</f>
         <v>14</v>
       </c>
       <c r="J6" s="1">
-        <f>'2017_IC3 State to City'!$G$31</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$31</f>
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <f>'2017_IC3 State to City'!$G$12</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$12</f>
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <f>'2017_IC3 State to City'!$G$15</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$15</f>
         <v>9</v>
       </c>
       <c r="M6" s="1">
-        <f>'2017_IC3 State to City'!$G$36</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$36</f>
         <v>11</v>
       </c>
       <c r="N6" s="1">
-        <f>'2017_IC3 State to City'!$G$18</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$18</f>
         <v>1</v>
       </c>
       <c r="O6" s="1">
-        <f>'2017_IC3 State to City'!$G$19</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$19</f>
         <v>11</v>
       </c>
       <c r="P6" s="1">
-        <f>'2017_IC3 State to City'!$G$8</f>
+        <f>'2017_IC3 State to City CALIFORN'!$G$8</f>
         <v>11</v>
       </c>
     </row>
@@ -20483,7 +20483,7 @@
         <v>2018</v>
       </c>
       <c r="C7" s="1">
-        <f>'2018_IC3 State to City'!$E$6</f>
+        <f>'2018_IC3 State to City CALIFORN'!$E$6</f>
         <v>181918</v>
       </c>
       <c r="D7" s="1">
@@ -20491,47 +20491,47 @@
         <v>2388</v>
       </c>
       <c r="F7" s="1">
-        <f>'2018_IC3 State to City'!$G$13</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$13</f>
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <f>'2018_IC3 State to City'!$G$29</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$29</f>
         <v>36</v>
       </c>
       <c r="H7" s="1">
-        <f>'2018_IC3 State to City'!$G$22</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$22</f>
         <v>1</v>
       </c>
       <c r="I7" s="1">
-        <f>'2018_IC3 State to City'!$G$30</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$30</f>
         <v>12</v>
       </c>
       <c r="J7" s="1">
-        <f>'2018_IC3 State to City'!$G$31</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$31</f>
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <f>'2018_IC3 State to City'!$G$12</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$12</f>
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <f>'2018_IC3 State to City'!$G$15</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$15</f>
         <v>37</v>
       </c>
       <c r="M7" s="1">
-        <f>'2018_IC3 State to City'!$G$36</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$36</f>
         <v>12</v>
       </c>
       <c r="N7" s="1">
-        <f>'2018_IC3 State to City'!$G$18</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$18</f>
         <v>1</v>
       </c>
       <c r="O7" s="1">
-        <f>'2018_IC3 State to City'!$G$19</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$19</f>
         <v>9</v>
       </c>
       <c r="P7" s="1">
-        <f>'2018_IC3 State to City'!$G$8</f>
+        <f>'2018_IC3 State to City CALIFORN'!$G$8</f>
         <v>13</v>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
         <v>2019</v>
       </c>
       <c r="C8" s="1">
-        <f>'2019_IC3 State to City'!$E$6</f>
+        <f>'2019_IC3 State to City CALIFORN'!$E$6</f>
         <v>182799</v>
       </c>
       <c r="D8" s="1">
@@ -20552,43 +20552,43 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <f>'2019_IC3 State to City'!$G$29</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$29</f>
         <v>24</v>
       </c>
       <c r="H8" s="1">
-        <f>'2019_IC3 State to City'!$G$22</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$22</f>
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <f>'2019_IC3 State to City'!$G$30</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$30</f>
         <v>12</v>
       </c>
       <c r="J8" s="1">
-        <f>'2019_IC3 State to City'!$G$31</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$31</f>
         <v>1</v>
       </c>
       <c r="K8" s="1">
-        <f>'2019_IC3 State to City'!$G$12</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$12</f>
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <f>'2019_IC3 State to City'!$G$15</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$15</f>
         <v>30</v>
       </c>
       <c r="M8" s="1">
-        <f>'2019_IC3 State to City'!$G$36</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$36</f>
         <v>10</v>
       </c>
       <c r="N8" s="1">
-        <f>'2019_IC3 State to City'!$G$18</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$18</f>
         <v>1</v>
       </c>
       <c r="O8" s="1">
-        <f>'2019_IC3 State to City'!$G$19</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$19</f>
         <v>8</v>
       </c>
       <c r="P8" s="1">
-        <f>'2019_IC3 State to City'!$G$8</f>
+        <f>'2019_IC3 State to City CALIFORN'!$G$8</f>
         <v>16</v>
       </c>
     </row>
@@ -20597,7 +20597,7 @@
         <v>2020</v>
       </c>
       <c r="C9" s="1">
-        <f>'2020_IC3 State to City'!$E$6</f>
+        <f>'2020_IC3 State to City CALIFORN'!$E$6</f>
         <v>181560</v>
       </c>
       <c r="D9" s="1">
@@ -20605,47 +20605,47 @@
         <v>-1239</v>
       </c>
       <c r="F9" s="1">
-        <f>'2020_IC3 State to City'!$G$13</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$13</f>
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <f>'2020_IC3 State to City'!$G$29</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$29</f>
         <v>29</v>
       </c>
       <c r="H9" s="1">
-        <f>'2020_IC3 State to City'!$G$22</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$22</f>
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <f>'2020_IC3 State to City'!$G$30</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$30</f>
         <v>15</v>
       </c>
       <c r="J9" s="1">
-        <f>'2020_IC3 State to City'!$G$31</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$31</f>
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <f>'2020_IC3 State to City'!$G$12</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$12</f>
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <f>'2020_IC3 State to City'!$G$15</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$15</f>
         <v>50</v>
       </c>
       <c r="M9" s="1">
-        <f>'2020_IC3 State to City'!$G$36</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$36</f>
         <v>13</v>
       </c>
       <c r="N9" s="1">
-        <f>'2020_IC3 State to City'!$G$18</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$18</f>
         <v>2</v>
       </c>
       <c r="O9" s="1">
-        <f>'2020_IC3 State to City'!$G$19</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$19</f>
         <v>15</v>
       </c>
       <c r="P9" s="1">
-        <f>'2020_IC3 State to City'!$G$8</f>
+        <f>'2020_IC3 State to City CALIFORN'!$G$8</f>
         <v>13</v>
       </c>
     </row>
@@ -20654,7 +20654,7 @@
         <v>2021</v>
       </c>
       <c r="C10" s="1">
-        <f>'2021_IC3 State to City'!$E$6</f>
+        <f>'2021_IC3 State to City CALIFORN'!$E$6</f>
         <v>181163</v>
       </c>
       <c r="D10" s="1">
@@ -20662,27 +20662,27 @@
         <v>-397</v>
       </c>
       <c r="F10" s="1">
-        <f>'2021_IC3 State to City'!$G$13</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$13</f>
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <f>'2021_IC3 State to City'!$G$29</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$29</f>
         <v>33</v>
       </c>
       <c r="H10" s="1">
-        <f>'2021_IC3 State to City'!$G$22</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$22</f>
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <f>'2021_IC3 State to City'!$G$30</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$30</f>
         <v>13</v>
       </c>
       <c r="J10" s="1">
-        <f>'2021_IC3 State to City'!$G$31</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$31</f>
         <v>2</v>
       </c>
       <c r="K10" s="1">
-        <f>'2021_IC3 State to City'!$G$12</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$12</f>
         <v>1</v>
       </c>
       <c r="L10">
@@ -20690,19 +20690,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <f>'2021_IC3 State to City'!$G$36</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$36</f>
         <v>8</v>
       </c>
       <c r="N10" s="1">
-        <f>'2021_IC3 State to City'!$G$18</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$18</f>
         <v>2</v>
       </c>
       <c r="O10" s="1">
-        <f>'2021_IC3 State to City'!$G$19</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$19</f>
         <v>17</v>
       </c>
       <c r="P10" s="1">
-        <f>'2021_IC3 State to City'!$G$8</f>
+        <f>'2021_IC3 State to City CALIFORN'!$G$8</f>
         <v>13</v>
       </c>
     </row>
@@ -20711,7 +20711,7 @@
         <v>2022</v>
       </c>
       <c r="C11" s="1">
-        <f>'2022_IC3 State to City'!$E$6</f>
+        <f>'2022_IC3 State to City CALIFORN'!$E$6</f>
         <v>184086</v>
       </c>
       <c r="D11" s="1">
@@ -20719,47 +20719,47 @@
         <v>2923</v>
       </c>
       <c r="F11" s="1">
-        <f>'2022_IC3 State to City'!$H$13</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$13</f>
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <f>'2022_IC3 State to City'!$H$29</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$29</f>
         <v>38</v>
       </c>
       <c r="H11" s="1">
-        <f>'2022_IC3 State to City'!$H$22</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$22</f>
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <f>'2022_IC3 State to City'!$H$30</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$30</f>
         <v>9</v>
       </c>
       <c r="J11" s="1">
-        <f>'2022_IC3 State to City'!$H$31</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$31</f>
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <f>'2022_IC3 State to City'!$H$12</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$12</f>
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <f>'2022_IC3 State to City'!$H$15</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$15</f>
         <v>22</v>
       </c>
       <c r="M11" s="1">
-        <f>'2022_IC3 State to City'!$H$36</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$36</f>
         <v>1</v>
       </c>
       <c r="N11" s="1">
-        <f>'2022_IC3 State to City'!$H$18</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$18</f>
         <v>1</v>
       </c>
       <c r="O11" s="1">
-        <f>'2022_IC3 State to City'!$H$19</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$19</f>
         <v>13</v>
       </c>
       <c r="P11" s="1">
-        <f>'2022_IC3 State to City'!$H$8</f>
+        <f>'2022_IC3 State to City CALIFORN'!$H$8</f>
         <v>15</v>
       </c>
     </row>
@@ -20963,48 +20963,48 @@
         <v>1368</v>
       </c>
       <c r="F7" s="3">
-        <f>E7/$E$5</f>
+        <f t="shared" ref="F7:F36" si="0">E7/$E$5</f>
         <v>3.4964546129137206E-5</v>
       </c>
-      <c r="G7" s="21">
-        <f>F7*$E$6</f>
+      <c r="G7" s="20">
+        <f t="shared" ref="G7:G36" si="1">F7*$E$6</f>
         <v>6.4364834387283514</v>
       </c>
       <c r="H7" s="1">
-        <f>ROUNDDOWN(G7,0)</f>
+        <f t="shared" ref="H7:H36" si="2">ROUNDDOWN(G7,0)</f>
         <v>6</v>
       </c>
       <c r="I7" s="10">
         <v>14557751</v>
       </c>
       <c r="J7" s="7">
-        <f>I7/E7</f>
+        <f t="shared" ref="J7:J36" si="3">I7/E7</f>
         <v>10641.630847953216</v>
       </c>
       <c r="K7" s="7">
-        <f>J7*H7</f>
+        <f t="shared" ref="K7:K36" si="4">J7*H7</f>
         <v>63849.785087719298</v>
       </c>
       <c r="L7" s="1">
         <v>618</v>
       </c>
       <c r="M7" s="3">
-        <f>L7/$E$5</f>
+        <f t="shared" ref="M7:M36" si="5">L7/$E$5</f>
         <v>1.579538706711023E-5</v>
       </c>
       <c r="N7" s="1">
-        <f>ROUNDDOWN(M7*$E$6,0)</f>
+        <f t="shared" ref="N7:N36" si="6">ROUNDDOWN(M7*$E$6,0)</f>
         <v>2</v>
       </c>
       <c r="O7" s="10">
         <v>6790738</v>
       </c>
       <c r="P7" s="7">
-        <f>O7/L7</f>
+        <f t="shared" ref="P7:P36" si="7">O7/L7</f>
         <v>10988.249190938512</v>
       </c>
       <c r="Q7" s="7">
-        <f>N7*P7</f>
+        <f t="shared" ref="Q7:Q36" si="8">N7*P7</f>
         <v>21976.498381877023</v>
       </c>
     </row>
@@ -21022,48 +21022,48 @@
         <v>3269</v>
       </c>
       <c r="F8" s="3">
-        <f>E8/$E$5</f>
+        <f t="shared" si="0"/>
         <v>8.3551974631688249E-5</v>
       </c>
-      <c r="G8" s="21">
-        <f>F8*$E$6</f>
+      <c r="G8" s="20">
+        <f t="shared" si="1"/>
         <v>15.380748802048963</v>
       </c>
       <c r="H8" s="1">
-        <f>ROUNDDOWN(G8,0)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I8" s="10">
         <v>439425357</v>
       </c>
       <c r="J8" s="7">
-        <f>I8/E8</f>
+        <f t="shared" si="3"/>
         <v>134421.95074946468</v>
       </c>
       <c r="K8" s="7">
-        <f>J8*H8</f>
+        <f t="shared" si="4"/>
         <v>2016329.2612419701</v>
       </c>
       <c r="L8" s="1">
         <v>616</v>
       </c>
       <c r="M8" s="3">
-        <f>L8/$E$5</f>
+        <f t="shared" si="5"/>
         <v>1.5744269309611491E-5</v>
       </c>
       <c r="N8" s="1">
-        <f>ROUNDDOWN(M8*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="O8" s="10">
         <v>96631599</v>
       </c>
       <c r="P8" s="7">
-        <f>O8/L8</f>
+        <f t="shared" si="7"/>
         <v>156869.47889610389</v>
       </c>
       <c r="Q8" s="7">
-        <f>N8*P8</f>
+        <f t="shared" si="8"/>
         <v>313738.95779220777</v>
       </c>
     </row>
@@ -21081,48 +21081,48 @@
         <v>74</v>
       </c>
       <c r="F9" s="3">
-        <f>E9/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.8913570274533283E-6</v>
       </c>
-      <c r="G9" s="21">
-        <f>F9*$E$6</f>
+      <c r="G9" s="20">
+        <f t="shared" si="1"/>
         <v>0.34817234975577338</v>
       </c>
       <c r="H9" s="1">
-        <f>ROUNDDOWN(G9,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="10">
         <v>9207962</v>
       </c>
       <c r="J9" s="7">
-        <f>I9/E9</f>
+        <f t="shared" si="3"/>
         <v>124431.91891891892</v>
       </c>
       <c r="K9" s="7">
-        <f>J9*H9</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
         <v>15</v>
       </c>
       <c r="M9" s="3">
-        <f>L9/$E$5</f>
+        <f t="shared" si="5"/>
         <v>3.8338318124053955E-7</v>
       </c>
       <c r="N9" s="1">
-        <f>ROUNDDOWN(M9*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O9" s="10">
         <v>103540</v>
       </c>
       <c r="P9" s="7">
-        <f>O9/L9</f>
+        <f t="shared" si="7"/>
         <v>6902.666666666667</v>
       </c>
       <c r="Q9" s="7">
-        <f>N9*P9</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21140,48 +21140,48 @@
         <v>2189</v>
       </c>
       <c r="F10" s="3">
-        <f>E10/$E$5</f>
+        <f t="shared" si="0"/>
         <v>5.5948385582369405E-5</v>
       </c>
-      <c r="G10" s="21">
-        <f>F10*$E$6</f>
+      <c r="G10" s="20">
+        <f t="shared" si="1"/>
         <v>10.299314508316055</v>
       </c>
       <c r="H10" s="1">
-        <f>ROUNDDOWN(G10,0)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I10" s="10">
         <v>158131770</v>
       </c>
       <c r="J10" s="7">
-        <f>I10/E10</f>
+        <f t="shared" si="3"/>
         <v>72239.273640931933</v>
       </c>
       <c r="K10" s="7">
-        <f>J10*H10</f>
+        <f t="shared" si="4"/>
         <v>722392.73640931933</v>
       </c>
       <c r="L10" s="1">
         <v>1109</v>
       </c>
       <c r="M10" s="3">
-        <f>L10/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.8344796533050555E-5</v>
       </c>
       <c r="N10" s="1">
-        <f>ROUNDDOWN(M10*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="O10" s="10">
         <v>79233267</v>
       </c>
       <c r="P10" s="7">
-        <f>O10/L10</f>
+        <f t="shared" si="7"/>
         <v>71445.687105500445</v>
       </c>
       <c r="Q10" s="7">
-        <f>N10*P10</f>
+        <f t="shared" si="8"/>
         <v>357228.43552750221</v>
       </c>
     </row>
@@ -21199,46 +21199,46 @@
         <v>2933</v>
       </c>
       <c r="F11" s="3">
-        <f>E11/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.4964191371900161E-5</v>
       </c>
-      <c r="G11" s="21">
-        <f>F11*$E$6</f>
+      <c r="G11" s="20">
+        <f t="shared" si="1"/>
         <v>13.799858132887612</v>
       </c>
       <c r="H11" s="1">
-        <f>ROUNDDOWN(G11,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="7">
-        <f>I11/E11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K11" s="7">
-        <f>J11*H11</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
         <v>1495</v>
       </c>
       <c r="M11" s="3">
-        <f>L11/$E$5</f>
+        <f t="shared" si="5"/>
         <v>3.821052373030711E-5</v>
       </c>
       <c r="N11" s="1">
-        <f>ROUNDDOWN(M11*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="O11" s="10">
         <v>19681014</v>
       </c>
       <c r="P11" s="7">
-        <f>O11/L11</f>
+        <f t="shared" si="7"/>
         <v>13164.557859531773</v>
       </c>
       <c r="Q11" s="7">
-        <f>N11*P11</f>
+        <f t="shared" si="8"/>
         <v>92151.905016722405</v>
       </c>
     </row>
@@ -21256,48 +21256,48 @@
         <v>256</v>
       </c>
       <c r="F12" s="3">
-        <f>E12/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.5430729598385414E-6</v>
       </c>
-      <c r="G12" s="21">
-        <f>F12*$E$6</f>
+      <c r="G12" s="20">
+        <f t="shared" si="1"/>
         <v>1.2044881288848377</v>
       </c>
       <c r="H12" s="1">
-        <f>ROUNDDOWN(G12,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I12" s="10">
         <v>87258</v>
       </c>
       <c r="J12" s="7">
-        <f>I12/E12</f>
+        <f t="shared" si="3"/>
         <v>340.8515625</v>
       </c>
       <c r="K12" s="7">
-        <f>J12*H12</f>
+        <f t="shared" si="4"/>
         <v>340.8515625</v>
       </c>
       <c r="L12" s="1">
         <v>78</v>
       </c>
       <c r="M12" s="3">
-        <f>L12/$E$5</f>
+        <f t="shared" si="5"/>
         <v>1.9935925424508054E-6</v>
       </c>
       <c r="N12" s="1">
-        <f>ROUNDDOWN(M12*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O12" s="10">
         <v>41012</v>
       </c>
       <c r="P12" s="7">
-        <f>O12/L12</f>
+        <f t="shared" si="7"/>
         <v>525.79487179487182</v>
       </c>
       <c r="Q12" s="7">
-        <f>N12*P12</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21315,48 +21315,48 @@
         <v>381</v>
       </c>
       <c r="F13" s="3">
-        <f>E13/$E$5</f>
+        <f t="shared" si="0"/>
         <v>9.7379328035097038E-6</v>
       </c>
-      <c r="G13" s="21">
-        <f>F13*$E$6</f>
+      <c r="G13" s="20">
+        <f t="shared" si="1"/>
         <v>1.7926170980668874</v>
       </c>
       <c r="H13" s="1">
-        <f>ROUNDDOWN(G13,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I13" s="10">
         <v>46132944</v>
       </c>
       <c r="J13" s="7">
-        <f>I13/E13</f>
+        <f t="shared" si="3"/>
         <v>121083.84251968504</v>
       </c>
       <c r="K13" s="7">
-        <f>J13*H13</f>
+        <f t="shared" si="4"/>
         <v>121083.84251968504</v>
       </c>
       <c r="L13" s="1">
         <v>131</v>
       </c>
       <c r="M13" s="3">
-        <f>L13/$E$5</f>
+        <f t="shared" si="5"/>
         <v>3.3482131161673785E-6</v>
       </c>
       <c r="N13" s="1">
-        <f>ROUNDDOWN(M13*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O13" s="10">
         <v>16578414</v>
       </c>
       <c r="P13" s="7">
-        <f>O13/L13</f>
+        <f t="shared" si="7"/>
         <v>126552.7786259542</v>
       </c>
       <c r="Q13" s="7">
-        <f>N13*P13</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21374,48 +21374,48 @@
         <v>1879</v>
       </c>
       <c r="F14" s="3">
-        <f>E14/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.8025133170064923E-5</v>
       </c>
-      <c r="G14" s="21">
-        <f>F14*$E$6</f>
+      <c r="G14" s="20">
+        <f t="shared" si="1"/>
         <v>8.8407546647445709</v>
       </c>
       <c r="H14" s="1">
-        <f>ROUNDDOWN(G14,0)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="I14" s="10">
         <v>6352139</v>
       </c>
       <c r="J14" s="7">
-        <f>I14/E14</f>
+        <f t="shared" si="3"/>
         <v>3380.5955295369877</v>
       </c>
       <c r="K14" s="7">
-        <f>J14*H14</f>
+        <f t="shared" si="4"/>
         <v>27044.764236295901</v>
       </c>
       <c r="L14" s="1">
         <v>931</v>
       </c>
       <c r="M14" s="3">
-        <f>L14/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.3795316115662819E-5</v>
       </c>
       <c r="N14" s="1">
-        <f>ROUNDDOWN(M14*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="O14" s="10">
         <v>4734064</v>
       </c>
       <c r="P14" s="7">
-        <f>O14/L14</f>
+        <f t="shared" si="7"/>
         <v>5084.9237379162187</v>
       </c>
       <c r="Q14" s="7">
-        <f>N14*P14</f>
+        <f t="shared" si="8"/>
         <v>20339.694951664875</v>
       </c>
     </row>
@@ -21433,48 +21433,48 @@
         <v>4746</v>
       </c>
       <c r="F15" s="3">
-        <f>E15/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.2130243854450671E-4</v>
       </c>
-      <c r="G15" s="21">
-        <f>F15*$E$6</f>
+      <c r="G15" s="20">
+        <f t="shared" si="1"/>
         <v>22.330080701904063</v>
       </c>
       <c r="H15" s="1">
-        <f>ROUNDDOWN(G15,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I15" s="10">
         <v>11064375</v>
       </c>
       <c r="J15" s="7">
-        <f>I15/E15</f>
+        <f t="shared" si="3"/>
         <v>2331.3053097345132</v>
       </c>
       <c r="K15" s="7">
-        <f>J15*H15</f>
+        <f t="shared" si="4"/>
         <v>51288.716814159292</v>
       </c>
       <c r="L15" s="1">
         <v>943</v>
       </c>
       <c r="M15" s="3">
-        <f>L15/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.4102022660655254E-5</v>
       </c>
       <c r="N15" s="1">
-        <f>ROUNDDOWN(M15*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="O15" s="10">
         <v>1746260</v>
       </c>
       <c r="P15" s="7">
-        <f>O15/L15</f>
+        <f t="shared" si="7"/>
         <v>1851.8133616118771</v>
       </c>
       <c r="Q15" s="7">
-        <f>N15*P15</f>
+        <f t="shared" si="8"/>
         <v>7407.2534464475084</v>
       </c>
     </row>
@@ -21492,48 +21492,48 @@
         <v>1285</v>
       </c>
       <c r="F16" s="3">
-        <f>E16/$E$5</f>
+        <f t="shared" si="0"/>
         <v>3.2843159192939555E-5</v>
       </c>
-      <c r="G16" s="21">
-        <f>F16*$E$6</f>
+      <c r="G16" s="20">
+        <f t="shared" si="1"/>
         <v>6.0459658031914714</v>
       </c>
       <c r="H16" s="1">
-        <f>ROUNDDOWN(G16,0)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="I16" s="11">
         <v>32297210</v>
       </c>
       <c r="J16" s="7">
-        <f>I16/E16</f>
+        <f t="shared" si="3"/>
         <v>25134.015564202335</v>
       </c>
       <c r="K16" s="7">
-        <f>J16*H16</f>
+        <f t="shared" si="4"/>
         <v>150804.09338521402</v>
       </c>
       <c r="L16" s="1">
         <v>255</v>
       </c>
       <c r="M16" s="3">
-        <f>L16/$E$5</f>
+        <f t="shared" si="5"/>
         <v>6.5175140810891718E-6</v>
       </c>
       <c r="N16" s="1">
-        <f>ROUNDDOWN(M16*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O16" s="10">
         <v>5168082</v>
       </c>
       <c r="P16" s="7">
-        <f>O16/L16</f>
+        <f t="shared" si="7"/>
         <v>20266.988235294117</v>
       </c>
       <c r="Q16" s="7">
-        <f>N16*P16</f>
+        <f t="shared" si="8"/>
         <v>20266.988235294117</v>
       </c>
     </row>
@@ -21551,46 +21551,46 @@
         <v>1693</v>
       </c>
       <c r="F17" s="3">
-        <f>E17/$E$5</f>
+        <f t="shared" si="0"/>
         <v>4.327118172268223E-5</v>
       </c>
-      <c r="G17" s="21">
-        <f>F17*$E$6</f>
+      <c r="G17" s="20">
+        <f t="shared" si="1"/>
         <v>7.9656187586016811</v>
       </c>
       <c r="H17" s="1">
-        <f>ROUNDDOWN(G17,0)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="I17" s="10">
         <v>1726392</v>
       </c>
       <c r="J17" s="7">
-        <f>I17/E17</f>
+        <f t="shared" si="3"/>
         <v>1019.7235676314235</v>
       </c>
       <c r="K17" s="7">
-        <f>J17*H17</f>
+        <f t="shared" si="4"/>
         <v>7138.0649734199651</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="3">
-        <f>L17/$E$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <f>ROUNDDOWN(M17*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O17" s="11">
         <v>219659</v>
       </c>
       <c r="P17" s="7" t="e">
-        <f>O17/L17</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q17" s="7" t="e">
-        <f>N17*P17</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -21608,48 +21608,48 @@
         <v>318</v>
       </c>
       <c r="F18" s="3">
-        <f>E18/$E$5</f>
+        <f t="shared" si="0"/>
         <v>8.1277234422994391E-6</v>
       </c>
-      <c r="G18" s="21">
-        <f>F18*$E$6</f>
+      <c r="G18" s="20">
+        <f t="shared" si="1"/>
         <v>1.4962000975991345</v>
       </c>
       <c r="H18" s="1">
-        <f>ROUNDDOWN(G18,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I18" s="10">
         <v>233333</v>
       </c>
       <c r="J18" s="7">
-        <f>I18/E18</f>
+        <f t="shared" si="3"/>
         <v>733.75157232704407</v>
       </c>
       <c r="K18" s="7">
-        <f>J18*H18</f>
+        <f t="shared" si="4"/>
         <v>733.75157232704407</v>
       </c>
       <c r="L18" s="1">
         <v>158</v>
       </c>
       <c r="M18" s="3">
-        <f>L18/$E$5</f>
+        <f t="shared" si="5"/>
         <v>4.03830284240035E-6</v>
       </c>
       <c r="N18" s="1">
-        <f>ROUNDDOWN(M18*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O18" s="10">
         <v>108269</v>
       </c>
       <c r="P18" s="7">
-        <f>O18/L18</f>
+        <f t="shared" si="7"/>
         <v>685.24683544303798</v>
       </c>
       <c r="Q18" s="7">
-        <f>N18*P18</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21667,48 +21667,48 @@
         <v>2854</v>
       </c>
       <c r="F19" s="3">
-        <f>E19/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.2945039950699989E-5</v>
       </c>
-      <c r="G19" s="21">
-        <f>F19*$E$6</f>
+      <c r="G19" s="20">
+        <f t="shared" si="1"/>
         <v>13.428160624364558</v>
       </c>
       <c r="H19" s="1">
-        <f>ROUNDDOWN(G19,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I19" s="10">
         <v>27903539</v>
       </c>
       <c r="J19" s="7">
-        <f>I19/E19</f>
+        <f t="shared" si="3"/>
         <v>9776.9933426769439</v>
       </c>
       <c r="K19" s="7">
-        <f>J19*H19</f>
+        <f t="shared" si="4"/>
         <v>127100.91345480028</v>
       </c>
       <c r="L19" s="1">
         <v>1075</v>
       </c>
       <c r="M19" s="3">
-        <f>L19/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.7475794655572001E-5</v>
       </c>
       <c r="N19" s="1">
-        <f>ROUNDDOWN(M19*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="O19" s="10">
         <v>13936804</v>
       </c>
       <c r="P19" s="7">
-        <f>O19/L19</f>
+        <f t="shared" si="7"/>
         <v>12964.468837209302</v>
       </c>
       <c r="Q19" s="7">
-        <f>N19*P19</f>
+        <f t="shared" si="8"/>
         <v>64822.34418604651</v>
       </c>
     </row>
@@ -21726,48 +21726,48 @@
         <v>4928</v>
       </c>
       <c r="F20" s="3">
-        <f>E20/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.2595415447689192E-4</v>
       </c>
-      <c r="G20" s="21">
-        <f>F20*$E$6</f>
+      <c r="G20" s="20">
+        <f t="shared" si="1"/>
         <v>23.186396481033128</v>
       </c>
       <c r="H20" s="1">
-        <f>ROUNDDOWN(G20,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="I20" s="10">
         <v>869614022</v>
       </c>
       <c r="J20" s="7">
-        <f>I20/E20</f>
+        <f t="shared" si="3"/>
         <v>176463.88433441558</v>
       </c>
       <c r="K20" s="7">
-        <f>J20*H20</f>
+        <f t="shared" si="4"/>
         <v>4058669.3396915584</v>
       </c>
       <c r="L20" s="1">
         <v>2308</v>
       </c>
       <c r="M20" s="3">
-        <f>L20/$E$5</f>
+        <f t="shared" si="5"/>
         <v>5.8989892153544353E-5</v>
       </c>
       <c r="N20" s="1">
-        <f>ROUNDDOWN(M20*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="O20" s="10">
         <v>396181523</v>
       </c>
       <c r="P20" s="7">
-        <f>O20/L20</f>
+        <f t="shared" si="7"/>
         <v>171655.7725303293</v>
       </c>
       <c r="Q20" s="7">
-        <f>N20*P20</f>
+        <f t="shared" si="8"/>
         <v>1716557.725303293</v>
       </c>
     </row>
@@ -21785,48 +21785,48 @@
         <v>453</v>
       </c>
       <c r="F21" s="3">
-        <f>E21/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.1578172073464295E-5</v>
       </c>
-      <c r="G21" s="21">
-        <f>F21*$E$6</f>
+      <c r="G21" s="20">
+        <f t="shared" si="1"/>
         <v>2.131379384315748</v>
       </c>
       <c r="H21" s="1">
-        <f>ROUNDDOWN(G21,0)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I21" s="10">
         <v>12243710</v>
       </c>
       <c r="J21" s="7">
-        <f>I21/E21</f>
+        <f t="shared" si="3"/>
         <v>27028.057395143489</v>
       </c>
       <c r="K21" s="7">
-        <f>J21*H21</f>
+        <f t="shared" si="4"/>
         <v>54056.114790286978</v>
       </c>
       <c r="L21" s="1">
         <v>201</v>
       </c>
       <c r="M21" s="3">
-        <f>L21/$E$5</f>
+        <f t="shared" si="5"/>
         <v>5.1373346286232297E-6</v>
       </c>
       <c r="N21" s="1">
-        <f>ROUNDDOWN(M21*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O21" s="10">
         <v>6236377</v>
       </c>
       <c r="P21" s="7">
-        <f>O21/L21</f>
+        <f t="shared" si="7"/>
         <v>31026.751243781095</v>
       </c>
       <c r="Q21" s="7">
-        <f>N21*P21</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21844,48 +21844,48 @@
         <v>94</v>
       </c>
       <c r="F22" s="3">
-        <f>E22/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.4025346024407144E-6</v>
       </c>
-      <c r="G22" s="21">
-        <f>F22*$E$6</f>
+      <c r="G22" s="20">
+        <f t="shared" si="1"/>
         <v>0.44227298482490135</v>
       </c>
       <c r="H22" s="1">
-        <f>ROUNDDOWN(G22,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I22" s="10">
         <v>138325</v>
       </c>
       <c r="J22" s="7">
-        <f>I22/E22</f>
+        <f t="shared" si="3"/>
         <v>1471.5425531914893</v>
       </c>
       <c r="K22" s="7">
-        <f>J22*H22</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
         <v>25</v>
       </c>
       <c r="M22" s="3">
-        <f>L22/$E$5</f>
+        <f t="shared" si="5"/>
         <v>6.3897196873423262E-7</v>
       </c>
       <c r="N22" s="1">
-        <f>ROUNDDOWN(M22*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="10">
         <v>178696</v>
       </c>
       <c r="P22" s="7">
-        <f>O22/L22</f>
+        <f t="shared" si="7"/>
         <v>7147.84</v>
       </c>
       <c r="Q22" s="7">
-        <f>N22*P22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -21903,48 +21903,48 @@
         <v>1</v>
       </c>
       <c r="F23" s="3">
-        <f>E23/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.5558878749369302E-8</v>
       </c>
-      <c r="G23" s="21">
-        <f>F23*$E$6</f>
+      <c r="G23" s="20">
+        <f t="shared" si="1"/>
         <v>4.7050317534563972E-3</v>
       </c>
       <c r="H23" s="1">
-        <f>ROUNDDOWN(G23,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="10">
         <v>0</v>
       </c>
       <c r="J23" s="7">
-        <f>I23/E23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K23" s="7">
-        <f>J23*H23</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <f>L23/$E$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <f>ROUNDDOWN(M23*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O23" s="10">
         <v>0</v>
       </c>
       <c r="P23" s="7" t="e">
-        <f>O23/L23</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q23" s="7" t="e">
-        <f>N23*P23</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -21962,48 +21962,48 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <f>E24/$E$5</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="21">
-        <f>F24*$E$6</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="20">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <f>ROUNDDOWN(G24,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I24" s="10">
         <v>0</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f>I24/E24</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="7" t="e">
-        <f>J24*H24</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <f>L24/$E$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f>ROUNDDOWN(M24*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O24" s="10">
         <v>0</v>
       </c>
       <c r="P24" s="7" t="e">
-        <f>O24/L24</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q24" s="7" t="e">
-        <f>N24*P24</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -22021,48 +22021,48 @@
         <v>28232</v>
       </c>
       <c r="F25" s="3">
-        <f>E25/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.2157826485219417E-4</v>
       </c>
-      <c r="G25" s="21">
-        <f>F25*$E$6</f>
+      <c r="G25" s="20">
+        <f t="shared" si="1"/>
         <v>132.83245646358102</v>
       </c>
       <c r="H25" s="1">
-        <f>ROUNDDOWN(G25,0)</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="I25" s="10">
         <v>0</v>
       </c>
       <c r="J25" s="7">
-        <f>I25/E25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K25" s="7">
-        <f>J25*H25</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
         <v>23222</v>
       </c>
       <c r="M25" s="3">
-        <f>L25/$E$5</f>
+        <f t="shared" si="5"/>
         <v>5.9352828231785395E-4</v>
       </c>
       <c r="N25" s="1">
-        <f>ROUNDDOWN(M25*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>109</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
       </c>
       <c r="P25" s="7">
-        <f>O25/L25</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q25" s="7">
-        <f>N25*P25</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -22080,48 +22080,48 @@
         <v>6624</v>
       </c>
       <c r="F26" s="3">
-        <f>E26/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.6930201283582225E-4</v>
       </c>
-      <c r="G26" s="21">
-        <f>F26*$E$6</f>
+      <c r="G26" s="20">
+        <f t="shared" si="1"/>
         <v>31.166130334895175</v>
       </c>
       <c r="H26" s="1">
-        <f>ROUNDDOWN(G26,0)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="I26" s="10">
         <v>41025991</v>
       </c>
       <c r="J26" s="7">
-        <f>I26/E26</f>
+        <f t="shared" si="3"/>
         <v>6193.5372886473433</v>
       </c>
       <c r="K26" s="7">
-        <f>J26*H26</f>
+        <f t="shared" si="4"/>
         <v>191999.65594806764</v>
       </c>
       <c r="L26" s="1">
         <v>3503</v>
       </c>
       <c r="M26" s="3">
-        <f>L26/$E$5</f>
+        <f t="shared" si="5"/>
         <v>8.9532752259040673E-5</v>
       </c>
       <c r="N26" s="1">
-        <f>ROUNDDOWN(M26*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O26" s="10">
         <v>23858715</v>
       </c>
       <c r="P26" s="7">
-        <f>O26/L26</f>
+        <f t="shared" si="7"/>
         <v>6810.9377676277472</v>
       </c>
       <c r="Q26" s="7">
-        <f>N26*P26</f>
+        <f t="shared" si="8"/>
         <v>108975.00428204396</v>
       </c>
     </row>
@@ -22139,48 +22139,48 @@
         <v>1173</v>
       </c>
       <c r="F27" s="3">
-        <f>E27/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.9980564773010193E-5</v>
       </c>
-      <c r="G27" s="21">
-        <f>F27*$E$6</f>
+      <c r="G27" s="20">
+        <f t="shared" si="1"/>
         <v>5.5190022468043543</v>
       </c>
       <c r="H27" s="1">
-        <f>ROUNDDOWN(G27,0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="I27" s="10">
         <v>18755779</v>
       </c>
       <c r="J27" s="7">
-        <f>I27/E27</f>
+        <f t="shared" si="3"/>
         <v>15989.581415174765</v>
       </c>
       <c r="K27" s="7">
-        <f>J27*H27</f>
+        <f t="shared" si="4"/>
         <v>79947.907075873823</v>
       </c>
       <c r="L27" s="1">
         <v>723</v>
       </c>
       <c r="M27" s="3">
-        <f>L27/$E$5</f>
+        <f t="shared" si="5"/>
         <v>1.8479069335794007E-5</v>
       </c>
       <c r="N27" s="1">
-        <f>ROUNDDOWN(M27*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="O27" s="10">
         <v>9906416</v>
       </c>
       <c r="P27" s="7">
-        <f>O27/L27</f>
+        <f t="shared" si="7"/>
         <v>13701.820193637621</v>
       </c>
       <c r="Q27" s="7">
-        <f>N27*P27</f>
+        <f t="shared" si="8"/>
         <v>41105.460580912862</v>
       </c>
     </row>
@@ -22198,48 +22198,48 @@
         <v>807</v>
       </c>
       <c r="F28" s="3">
-        <f>E28/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.0626015150741029E-5</v>
       </c>
-      <c r="G28" s="21">
-        <f>F28*$E$6</f>
+      <c r="G28" s="20">
+        <f t="shared" si="1"/>
         <v>3.7969606250393131</v>
       </c>
       <c r="H28" s="1">
-        <f>ROUNDDOWN(G28,0)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="I28" s="10">
         <v>4754892</v>
       </c>
       <c r="J28" s="7">
-        <f>I28/E28</f>
+        <f t="shared" si="3"/>
         <v>5892.0594795539037</v>
       </c>
       <c r="K28" s="7">
-        <f>J28*H28</f>
+        <f t="shared" si="4"/>
         <v>17676.178438661711</v>
       </c>
       <c r="L28" s="1">
         <v>344</v>
       </c>
       <c r="M28" s="3">
-        <f>L28/$E$5</f>
+        <f t="shared" si="5"/>
         <v>8.7922542897830406E-6</v>
       </c>
       <c r="N28" s="1">
-        <f>ROUNDDOWN(M28*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O28" s="10">
         <v>1726660</v>
       </c>
       <c r="P28" s="7">
-        <f>O28/L28</f>
+        <f t="shared" si="7"/>
         <v>5019.3604651162786</v>
       </c>
       <c r="Q28" s="7">
-        <f>N28*P28</f>
+        <f t="shared" si="8"/>
         <v>5019.3604651162786</v>
       </c>
     </row>
@@ -22257,48 +22257,48 @@
         <v>8196</v>
       </c>
       <c r="F29" s="3">
-        <f>E29/$E$5</f>
+        <f t="shared" si="0"/>
         <v>2.0948057022983081E-4</v>
       </c>
-      <c r="G29" s="21">
-        <f>F29*$E$6</f>
+      <c r="G29" s="20">
+        <f t="shared" si="1"/>
         <v>38.562440251328631</v>
       </c>
       <c r="H29" s="1">
-        <f>ROUNDDOWN(G29,0)</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="I29" s="10">
         <v>153022651</v>
       </c>
       <c r="J29" s="7">
-        <f>I29/E29</f>
+        <f t="shared" si="3"/>
         <v>18670.406417764763</v>
       </c>
       <c r="K29" s="7">
-        <f>J29*H29</f>
+        <f t="shared" si="4"/>
         <v>709475.443875061</v>
       </c>
       <c r="L29" s="1">
         <v>3238</v>
       </c>
       <c r="M29" s="3">
-        <f>L29/$E$5</f>
+        <f t="shared" si="5"/>
         <v>8.2759649390457801E-5</v>
       </c>
       <c r="N29" s="1">
-        <f>ROUNDDOWN(M29*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O29" s="10">
         <v>35649051</v>
       </c>
       <c r="P29" s="7">
-        <f>O29/L29</f>
+        <f t="shared" si="7"/>
         <v>11009.589561457689</v>
       </c>
       <c r="Q29" s="7">
-        <f>N29*P29</f>
+        <f t="shared" si="8"/>
         <v>165143.84342186534</v>
       </c>
     </row>
@@ -22316,48 +22316,48 @@
         <v>2041</v>
       </c>
       <c r="F30" s="3">
-        <f>E30/$E$5</f>
+        <f t="shared" si="0"/>
         <v>5.2165671527462746E-5</v>
       </c>
-      <c r="G30" s="21">
-        <f>F30*$E$6</f>
+      <c r="G30" s="20">
+        <f t="shared" si="1"/>
         <v>9.6029698088045077</v>
       </c>
       <c r="H30" s="1">
-        <f>ROUNDDOWN(G30,0)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I30" s="10">
         <v>14628440</v>
       </c>
       <c r="J30" s="7">
-        <f>I30/E30</f>
+        <f t="shared" si="3"/>
         <v>7167.2905438510534</v>
       </c>
       <c r="K30" s="7">
-        <f>J30*H30</f>
+        <f t="shared" si="4"/>
         <v>64505.614894659477</v>
       </c>
       <c r="L30" s="1">
         <v>552</v>
       </c>
       <c r="M30" s="3">
-        <f>L30/$E$5</f>
+        <f t="shared" si="5"/>
         <v>1.4108501069651855E-5</v>
       </c>
       <c r="N30" s="1">
-        <f>ROUNDDOWN(M30*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="O30" s="10">
         <v>1354479</v>
       </c>
       <c r="P30" s="7">
-        <f>O30/L30</f>
+        <f t="shared" si="7"/>
         <v>2453.766304347826</v>
       </c>
       <c r="Q30" s="7">
-        <f>N30*P30</f>
+        <f t="shared" si="8"/>
         <v>4907.532608695652</v>
       </c>
     </row>
@@ -22375,48 +22375,48 @@
         <v>296</v>
       </c>
       <c r="F31" s="3">
-        <f>E31/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.5654281098133132E-6</v>
       </c>
-      <c r="G31" s="21">
-        <f>F31*$E$6</f>
+      <c r="G31" s="20">
+        <f t="shared" si="1"/>
         <v>1.3926893990230935</v>
       </c>
       <c r="H31" s="1">
-        <f>ROUNDDOWN(G31,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I31" s="10">
         <v>1945212</v>
       </c>
       <c r="J31" s="7">
-        <f>I31/E31</f>
+        <f t="shared" si="3"/>
         <v>6571.6621621621625</v>
       </c>
       <c r="K31" s="7">
-        <f>J31*H31</f>
+        <f t="shared" si="4"/>
         <v>6571.6621621621625</v>
       </c>
       <c r="L31" s="1">
         <v>19</v>
       </c>
       <c r="M31" s="3">
-        <f>L31/$E$5</f>
+        <f t="shared" si="5"/>
         <v>4.856186962380168E-7</v>
       </c>
       <c r="N31" s="1">
-        <f>ROUNDDOWN(M31*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O31" s="10">
         <v>700000</v>
       </c>
       <c r="P31" s="7">
-        <f>O31/L31</f>
+        <f t="shared" si="7"/>
         <v>36842.105263157893</v>
       </c>
       <c r="Q31" s="7">
-        <f>N31*P31</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -22434,46 +22434,46 @@
         <v>2126</v>
       </c>
       <c r="F32" s="3">
-        <f>E32/$E$5</f>
+        <f t="shared" si="0"/>
         <v>5.4338176221159139E-5</v>
       </c>
-      <c r="G32" s="21">
-        <f>F32*$E$6</f>
+      <c r="G32" s="20">
+        <f t="shared" si="1"/>
         <v>10.002897507848301</v>
       </c>
       <c r="H32" s="1">
-        <f>ROUNDDOWN(G32,0)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I32" s="10">
         <v>62209889</v>
       </c>
       <c r="J32" s="7">
-        <f>I32/E32</f>
+        <f t="shared" si="3"/>
         <v>29261.47177798683</v>
       </c>
       <c r="K32" s="7">
-        <f>J32*H32</f>
+        <f t="shared" si="4"/>
         <v>292614.71777986828</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="3">
-        <f>L32/$E$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <f>ROUNDDOWN(M32*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O32" s="10">
         <v>17908856</v>
       </c>
       <c r="P32" s="7" t="e">
-        <f>O32/L32</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q32" s="7" t="e">
-        <f>N32*P32</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -22491,48 +22491,48 @@
         <v>355</v>
       </c>
       <c r="F33" s="3">
-        <f>E33/$E$5</f>
+        <f t="shared" si="0"/>
         <v>9.0734019560261023E-6</v>
       </c>
-      <c r="G33" s="21">
-        <f>F33*$E$6</f>
+      <c r="G33" s="20">
+        <f t="shared" si="1"/>
         <v>1.6702862724770211</v>
       </c>
       <c r="H33" s="1">
-        <f>ROUNDDOWN(G33,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I33" s="10">
         <v>14258872</v>
       </c>
       <c r="J33" s="7">
-        <f>I33/E33</f>
+        <f t="shared" si="3"/>
         <v>40165.836619718313</v>
       </c>
       <c r="K33" s="7">
-        <f>J33*H33</f>
+        <f t="shared" si="4"/>
         <v>40165.836619718313</v>
       </c>
       <c r="L33" s="1">
         <v>97</v>
       </c>
       <c r="M33" s="3">
-        <f>L33/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.4792112386888222E-6</v>
       </c>
       <c r="N33" s="1">
-        <f>ROUNDDOWN(M33*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O33" s="10">
         <v>2884955</v>
       </c>
       <c r="P33" s="7">
-        <f>O33/L33</f>
+        <f t="shared" si="7"/>
         <v>29741.804123711339</v>
       </c>
       <c r="Q33" s="7">
-        <f>N33*P33</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -22550,48 +22550,48 @@
         <v>2615</v>
       </c>
       <c r="F34" s="3">
-        <f>E34/$E$5</f>
+        <f t="shared" si="0"/>
         <v>6.6836467929600729E-5</v>
       </c>
-      <c r="G34" s="21">
-        <f>F34*$E$6</f>
+      <c r="G34" s="20">
+        <f t="shared" si="1"/>
         <v>12.30365803528848</v>
       </c>
       <c r="H34" s="1">
-        <f>ROUNDDOWN(G34,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I34" s="10">
         <v>17907024</v>
       </c>
       <c r="J34" s="7">
-        <f>I34/E34</f>
+        <f t="shared" si="3"/>
         <v>6847.8103250478016</v>
       </c>
       <c r="K34" s="7">
-        <f>J34*H34</f>
+        <f t="shared" si="4"/>
         <v>82173.723900573619</v>
       </c>
       <c r="L34" s="1">
         <v>745</v>
       </c>
       <c r="M34" s="3">
-        <f>L34/$E$5</f>
+        <f t="shared" si="5"/>
         <v>1.904136466828013E-5</v>
       </c>
       <c r="N34" s="1">
-        <f>ROUNDDOWN(M34*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="O34" s="10">
         <v>4705608</v>
       </c>
       <c r="P34" s="7">
-        <f>O34/L34</f>
+        <f t="shared" si="7"/>
         <v>6316.2523489932883</v>
       </c>
       <c r="Q34" s="7">
-        <f>N34*P34</f>
+        <f t="shared" si="8"/>
         <v>18948.757046979867</v>
       </c>
     </row>
@@ -22609,48 +22609,48 @@
         <v>4488</v>
       </c>
       <c r="F35" s="3">
-        <f>E35/$E$5</f>
+        <f t="shared" si="0"/>
         <v>1.1470824782716943E-4</v>
       </c>
-      <c r="G35" s="21">
-        <f>F35*$E$6</f>
+      <c r="G35" s="20">
+        <f t="shared" si="1"/>
         <v>21.116182509512313</v>
       </c>
       <c r="H35" s="1">
-        <f>ROUNDDOWN(G35,0)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I35" s="10">
         <v>128250735</v>
       </c>
       <c r="J35" s="7">
-        <f>I35/E35</f>
+        <f t="shared" si="3"/>
         <v>28576.366978609625</v>
       </c>
       <c r="K35" s="7">
-        <f>J35*H35</f>
+        <f t="shared" si="4"/>
         <v>600103.7065508021</v>
       </c>
       <c r="L35" s="1">
         <v>1633</v>
       </c>
       <c r="M35" s="3">
-        <f>L35/$E$5</f>
+        <f t="shared" si="5"/>
         <v>4.1737648997720071E-5</v>
       </c>
       <c r="N35" s="1">
-        <f>ROUNDDOWN(M35*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="O35" s="10">
         <v>74236808</v>
       </c>
       <c r="P35" s="7">
-        <f>O35/L35</f>
+        <f t="shared" si="7"/>
         <v>45460.384568279238</v>
       </c>
       <c r="Q35" s="7">
-        <f>N35*P35</f>
+        <f t="shared" si="8"/>
         <v>318222.69197795464</v>
       </c>
     </row>
@@ -22668,48 +22668,48 @@
         <v>295</v>
       </c>
       <c r="F36" s="3">
-        <f>E36/$E$5</f>
+        <f t="shared" si="0"/>
         <v>7.5398692310639445E-6</v>
       </c>
-      <c r="G36" s="21">
-        <f>F36*$E$6</f>
+      <c r="G36" s="20">
+        <f t="shared" si="1"/>
         <v>1.3879843672696373</v>
       </c>
       <c r="H36" s="1">
-        <f>ROUNDDOWN(G36,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I36" s="10">
         <v>421261</v>
       </c>
       <c r="J36" s="7">
-        <f>I36/E36</f>
+        <f t="shared" si="3"/>
         <v>1428.0033898305085</v>
       </c>
       <c r="K36" s="7">
-        <f>J36*H36</f>
+        <f t="shared" si="4"/>
         <v>1428.0033898305085</v>
       </c>
       <c r="L36" s="1">
         <v>115</v>
       </c>
       <c r="M36" s="3">
-        <f>L36/$E$5</f>
+        <f t="shared" si="5"/>
         <v>2.9392710561774699E-6</v>
       </c>
       <c r="N36" s="1">
-        <f>ROUNDDOWN(M36*$E$6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O36" s="10">
         <v>120904</v>
       </c>
       <c r="P36" s="7">
-        <f>O36/L36</f>
+        <f t="shared" si="7"/>
         <v>1051.3391304347826</v>
       </c>
       <c r="Q36" s="7">
-        <f>N36*P36</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="7">
-        <f t="shared" ref="K37:K38" si="0">J37*H37</f>
+        <f t="shared" ref="K37:K38" si="9">J37*H37</f>
         <v>0</v>
       </c>
       <c r="M37" s="3"/>
@@ -22745,11 +22745,11 @@
         <v>#REF!</v>
       </c>
       <c r="J38" s="7" t="e">
-        <f t="shared" ref="J9:J38" si="1">I38/E38</f>
+        <f t="shared" ref="J38" si="10">I38/E38</f>
         <v>#REF!</v>
       </c>
       <c r="K38" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>#REF!</v>
       </c>
       <c r="M38" s="3"/>
